--- a/Застосовне законодавство.xlsx
+++ b/Застосовне законодавство.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\x\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\x\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09D378CF-225C-4AB6-83C2-45D411876FD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B79DD0D-D8B9-4BD0-9F26-ABC3AE3D7A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{334805C5-B449-4CB8-AF80-1835CA06DE69}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="583">
   <si>
     <t>- В цьому реєстрі перераховані тільки основні законодавчі акти, не враховуючи супутні акти, що затверджують зміни, або покладають завдання з реалізації, наприклад, Національної стратегії кібербезпеки.
 - Сайт ВРУ - основне джерело інформації, оскільки на ньому можна відстежувати актуальність законодавчих актів.</t>
@@ -1754,13 +1754,108 @@
     <t>наказ Адміністрації Держспецзв’язку від 11.07.2025 року № 438 «Про затвердження Вимог до юридичних осіб, фізичних осіб-підприємців, які здійснюють оцінювання реалізації цільового профілю безпеки інформаційних, електронних комунікаційних, інформаційно-комунікаційних, технологічних систем», зареєстрований у Міністерстві юстиції України 31 липня 2025 року за № 1125/44531;</t>
   </si>
   <si>
-    <t>https://cip.gov.ua/ua/news/administraciyeyu-derzhspeczv-yazku-priinyato-vimogi-do-yuridichnikh-osib-fizichnikh-osib-pidpriyemciv-yaki-zdiisnyuyut-ocinyuvannya-realizaciyi-cilovogo-profilyu-bezpeki-informaciinikh-elektronnikh-komunikaciinikh-informaciino-komunikaciinikh-tekhnologichnikh-sistem?fbclid=IwY2xjawPAxYtleHRuA2FlbQIxMABicmlkETFIeUlOVG5yeE02a0pSYko2c3J0YwZhcHBfaWQQMjIyMDM5MTc4ODIwMDg5MgABHowrVHZFOGs4IsyXjGbN7rSHg-Yu91NABS1TRN-xKMxjFeNG-RbpxZLCDD5Q_aem_ddGGwzZhgzQ_4NY6Iysopg</t>
-  </si>
-  <si>
     <t>https://cip.gov.ua/ua/news/perelik-normativno-pravovikh-aktiv-na-vikonannya-zakonu-4336-ix</t>
   </si>
   <si>
     <t>Перелік нормативно-правових актів на виконання Закону № 4336-IX</t>
+  </si>
+  <si>
+    <t>https://cip.gov.ua/ua/news/administraciyeyu-derzhspeczv-yazku-priinyato-vimogi-do-yuridichnikh-osib-fizichnikh-osib-pidpriyemciv-yaki-zdiisnyuyut-ocinyuvannya-realizaciyi-cilovogo-profilyu-bezpeki-informaciinikh-elektronnikh-komunikaciinikh-informaciino-komunikaciinikh-tekhnologichnikh-sistem</t>
+  </si>
+  <si>
+    <t>Наказ Адміністрації Держспецзв’язку від 21.01.2026 № 44 "Про затвердження форми повідомлення про внесення відомостей щодо об’єкта критичної інформаційної інфраструктури до державного реєстру об’єктів критичної інформаційної інфраструктури"</t>
+  </si>
+  <si>
+    <t>https://cip.gov.ua/ua/news/nakaz-administraciyi-derzhspeczv-yazku-vid-21-01-2026-44-pro-zatverdzhennya-formi-povidomlennya-pro-vnesennya-vidomostei-shodo-ob-yekta-kritichnoyi-informaciinoyi-infrastrukturi-do-derzhavnogo-reyestru-ob-yektiv-kritichnoyi-informaciinoyi-infrastrukturi</t>
+  </si>
+  <si>
+    <t>Наказ Адміністрації Держспецзв’язку від 30.01.2026 № 75 «Про затвердження Каталогу заходів з кіберзахисту, базових заходів з кіберзахисту, форми плану кіберзахисту та методичних рекомендацій щодо здійснення заходів з кіберзахисту»</t>
+  </si>
+  <si>
+    <t>Оновлений переклад NIST CSF 2.0.</t>
+  </si>
+  <si>
+    <t>https://cip.gov.ua/ua/news/nakaz-administraciyi-derzhspeczv-yazku-vid-30-01-2026-75-pro-zatverdzhennya-katalogu-zakhodiv-z-kiberzakhistu-bazovikh-zakhodiv-z-kiberzakhistu-formi-planu-kiberzakhistu-ta-metodichnikh-rekomendacii-shodo-zdiisnennya-zakhodiv-z-kiberzakhistu</t>
+  </si>
+  <si>
+    <t>Наказ Адміністрації Держспецзв’язку від 18.02.2026 № 141 «Про затвердження Примірної публічної пропозиції про здійснення пошуку та виявлення потенційної вразливості ...»</t>
+  </si>
+  <si>
+    <t>Наказ Адміністрації Держспецзв’язку від 18.02.2026 № 143 «Деякі питання реагування на кіберінциденти, кібератаки та кіберзагрози»</t>
+  </si>
+  <si>
+    <t>https://cip.gov.ua/ua/news/nakaz-administraciyi-derzhspeczv-yazku-vid-18-02-2026-141-pro-zatverdzhennya-primirnoyi-publichnoyi-propoziciyi-pro-zdiisnennya-poshuku-ta-viyavlennya-potenciinoyi-vrazlivosti</t>
+  </si>
+  <si>
+    <t>https://cip.gov.ua/ua/news/nakaz-administraciyi-derzhspeczv-yazku-vid-18-02-2026-143-deyaki-pitannya-reaguvannya-na-kiberincidenti-kiberataki-ta-kiberzagrozi</t>
+  </si>
+  <si>
+    <t>https://cip.gov.ua/ua/news/nakaz-administraciyi-derzhspeczv-yazku-vid-23-02-2026-154-pro-zatverdzhennya-rekomendacii-z-kiberzakhistu-informaciino-komunikaciinikh-sistem-yaki-vikoristovuyut-tekhnologiyi-shtuchnogo-intelektu</t>
+  </si>
+  <si>
+    <t>Наказ Адміністрації Держспецзв’язку від 23.02.2026 № 154 «Про затвердження Рекомендацій з кіберзахисту інформаційно-комунікаційних систем, які використовують технології штучного інтелекту»</t>
+  </si>
+  <si>
+    <t>Документ розроблено як практичний орієнтир для власників та розпорядників державних і приватних інформаційних, електронних комунікаційних та технологічних систем. Рекомендації мають добровільний характер і призначені для використання під час розробки планів кіберзахисту та оцінки ризиків при впровадженні технологій ШІ.
+Документ пропонує комплексний підхід до безпечного впровадження ШІ та деталізує таксономію специфічних кіберзагроз, характерних саме для таких систем, а також кроки для їх нейтралізації.</t>
+  </si>
+  <si>
+    <t>https://zakon.rada.gov.ua/laws/show/75-2025-%D0%BF#Text</t>
+  </si>
+  <si>
+    <t>Цей Порядок визначає процедури здійснення заходів з підготовки електронних комунікаційних мереж загального користування до функціонування в умовах надзвичайної ситуації, надзвичайного або воєнного стану, механізми здійснення їх оперативно-технічного управління, повноваження суб’єктів системи оперативно-технічного управління електронними комунікаційними мережами загального користування та умови їх взаємодії щодо надання електронних комунікаційних послуг для цілей оборони та безпеки держави в умовах надзвичайної ситуації, надзвичайного або воєнного стану, обсяги та строки подання інформації постачальниками електронних комунікаційних мереж та/або послуг про електронні комунікаційні мережі, які вони експлуатують, до Національного центру оперативно-технічного управління електронними комунікаційними мережами України (далі - Національний центр).</t>
+  </si>
+  <si>
+    <t>Постанова Кабінету Міністрів України від 24.01.2025 № 75 "Деякі питання оперативно-технічного управління електронними комунікаційними мережами в умовах надзвичайної ситуації, надзвичайного або воєнного стану"</t>
+  </si>
+  <si>
+    <t>Наказ Адміністрації Держспецзв’язку від 28 січня 2026 року № 67/ДСК, зареєстрований у Міністерстві юстиції України 9 лютого 2026 року за № 174/45568.</t>
+  </si>
+  <si>
+    <t>https://cip.gov.ua/ua/news/unormovano-poryadok-nadannya-i-vikoristannya-poslug-elektronnoyi-identifikaciyi-ta-elektronnikh-dovirchikh-poslug-pri-obrobci-sluzhbovoyi-informaciyi-i-derzhtayemnici</t>
+  </si>
+  <si>
+    <t>Наказ встановлює порядок надання та використання послуг електронної ідентифікації та електронних довірчих послуг в інформаційно-комунікаційних системах, у яких обробляються службова інформація та державна таємниця.</t>
+  </si>
+  <si>
+    <t>Цей наказ замінює попередні рекомендації 2023 року та впроваджує сучасний ризикоорієнтований підхід, побудований на основі європейських стандартів і кращих світових практик. ова нормативна база покликана не просто оновити термінологію, а й змінити фокус з виключно реактивних дій на проактивне управління ризиками. Саме тому до звичних понять кіберінцидентів та кібератак у документі додано роботу з кіберзагрозами. Це дає можливість виявляти та нейтралізувати небезпеку ще до того, як вона завдасть реальної шкоди системам та мережам.</t>
+  </si>
+  <si>
+    <t>Інтернет провайдери</t>
+  </si>
+  <si>
+    <t>https://zakon.rada.gov.ua/laws/show/z1978-25#Text</t>
+  </si>
+  <si>
+    <t>Наказ Адміністрації Держспецзв’язку від від 17.12.2025 № 836 "Порядок
+підтвердження постачальниками товарів, робіт, послуг відповідності впроваджених заходів безпеки інформації встановленим вимогам відповідно до рівня ризику, пов’язаного з постачанням товарів, робіт, послуг власникам або розпорядникам інформаційно-комунікаційних систем, у яких обробляються державні інформаційні ресурси або службова інформація та інформація, що становить державну таємницю, об’єктів критичної інформаційної інфраструктури"</t>
+  </si>
+  <si>
+    <t>Цей Порядок встановлює процедуру підтвердження постачальниками товарів, робіт, послуг відповідності впроваджених заходів безпеки інформації встановленим вимогам відповідно до рівня ризику, пов’язаного з постачанням товарів, робіт, послуг власникам або розпорядникам інформаційно-комунікаційних систем, у яких обробляються державні інформаційні ресурси або службова інформація та інформація, що становить державну таємницю, об’єктів критичної інформаційної інфраструктури (далі — системи).</t>
+  </si>
+  <si>
+    <t>Наказ Адміністрації Держспецзв’язку від 05 серпня 2025 р. № 482 «Про затвердження Методичних рекомендацій щодо збору та обробки статистичних даних стосовно кібератак, кіберінцидентів і заходів протидії у Державній службі спеціального зв’язку та захисту інформації України»;</t>
+  </si>
+  <si>
+    <t>https://cip.gov.ua/ua/docs/nakaz-administraciyi-derzhspeczv-yazku-vid-05-08-2025-482-pro-zatverdzhennya-metodichnikh-rekomendacii-shodo-zboru-ta-obrobki-statistichnikh-danikh-stosovno-kiberatak-kiberincidentiv-i-zakhodiv-protidiyi-u-derzhavnii-sluzhbi-specialnogo-zv-yazku-ta-zakhistu-informaciyi-ukrayini</t>
+  </si>
+  <si>
+    <t>Документ встановлює чіткий механізм контролю за станом безпеки інформаційних, електронних комунікаційних, інформаційно-комунікаційних та технологічних систем. Йдеться про системи, що внесені до переліку авторизованих і належать до об’єктів критичної інформаційної інфраструктури або оперують даними, захист яких гарантується законом.</t>
+  </si>
+  <si>
+    <t>https://zakon.rada.gov.ua/laws/show/z0008-26#Text</t>
+  </si>
+  <si>
+    <t>Наказ Адміністрації Держспецзв’язку від 19 грудня 2025 року № 847 зареєстровано у Міністерстві юстиції України 5 січня 2026 року за № 8/45402 "Про затвердження Порядку здійснення моніторингу авторизації з безпеки інформаційних, електронних комунікаційних, інформаційно-комунікаційних, технологічних систем"</t>
+  </si>
+  <si>
+    <t>https://zakon.rada.gov.ua/laws/show/712-2025-%D0%BF#n18</t>
+  </si>
+  <si>
+    <t>Постанова Кабінету Міністрів України від 18.06.2025 № 712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Цей Порядок визначає процедури проведення авторизації з безпеки інформаційних, електронних комунікаційних, інформаційно-комунікаційних, технологічних систем, в яких обробляються державні інформаційні ресурси або інформація з обмеженим доступом, вимога щодо захисту якої встановлена законом, об’єктів критичної інформаційної інфраструктури, власниками або розпорядниками яких є органи державної влади, інші державні органи, державні підприємства, установи та організації, органи місцевого самоврядування (далі - системи), а також підтвердження дотримання вимог з безпеки щодо таких систем протягом їх життєвого циклу. </t>
   </si>
 </sst>
 </file>
@@ -1939,7 +2034,187 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="53">
+  <dxfs count="69">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -2837,21 +3112,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FE4F2F92-58E2-48B9-A7D4-627EBB6ED48E}" name="Таблиця2" displayName="Таблиця2" ref="B18:J228" totalsRowShown="0" headerRowDxfId="52" dataDxfId="50" headerRowBorderDxfId="51" tableBorderDxfId="49">
-  <autoFilter ref="B18:J228" xr:uid="{FE4F2F92-58E2-48B9-A7D4-627EBB6ED48E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FE4F2F92-58E2-48B9-A7D4-627EBB6ED48E}" name="Таблиця2" displayName="Таблиця2" ref="B18:J239" totalsRowShown="0" headerRowDxfId="68" dataDxfId="66" headerRowBorderDxfId="67" tableBorderDxfId="65">
+  <autoFilter ref="B18:J239" xr:uid="{FE4F2F92-58E2-48B9-A7D4-627EBB6ED48E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B19:I200">
     <sortCondition ref="B18:B200"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{DFA9E46C-509D-4A00-A369-7966EED6B176}" name="№" dataDxfId="48"/>
-    <tableColumn id="2" xr3:uid="{981014D8-EFBF-47F5-B054-36010B7987AF}" name="Джерело вимог" dataDxfId="47"/>
-    <tableColumn id="3" xr3:uid="{928FBB84-B24F-469A-AFD2-7EA49120BF89}" name="Посилання" dataDxfId="46"/>
-    <tableColumn id="4" xr3:uid="{D49602E6-E651-4C6D-8A88-C8DCD8A3AFDD}" name="Коментар" dataDxfId="45"/>
-    <tableColumn id="6" xr3:uid="{52AE3B44-6A02-4F51-99B9-C7E17C080BEC}" name="Категорія" dataDxfId="44"/>
-    <tableColumn id="8" xr3:uid="{DE39899F-E232-40DC-A0D1-10B3A973A842}" name="Застосовність" dataDxfId="43"/>
-    <tableColumn id="10" xr3:uid="{40F3EA47-8E92-48F7-A24A-6369E84EA096}" name="Теги" dataDxfId="42"/>
-    <tableColumn id="5" xr3:uid="{A1D4F9E4-94BB-4008-834E-B5DC4DE59C40}" name="Дата прийняття" dataDxfId="41"/>
-    <tableColumn id="7" xr3:uid="{2B27F073-AE91-4210-B0D6-642DEFE05F63}" name="Галузь" dataDxfId="40"/>
+    <tableColumn id="1" xr3:uid="{DFA9E46C-509D-4A00-A369-7966EED6B176}" name="№" dataDxfId="64"/>
+    <tableColumn id="2" xr3:uid="{981014D8-EFBF-47F5-B054-36010B7987AF}" name="Джерело вимог" dataDxfId="63"/>
+    <tableColumn id="3" xr3:uid="{928FBB84-B24F-469A-AFD2-7EA49120BF89}" name="Посилання" dataDxfId="62"/>
+    <tableColumn id="4" xr3:uid="{D49602E6-E651-4C6D-8A88-C8DCD8A3AFDD}" name="Коментар" dataDxfId="61"/>
+    <tableColumn id="6" xr3:uid="{52AE3B44-6A02-4F51-99B9-C7E17C080BEC}" name="Категорія" dataDxfId="60"/>
+    <tableColumn id="8" xr3:uid="{DE39899F-E232-40DC-A0D1-10B3A973A842}" name="Застосовність" dataDxfId="59"/>
+    <tableColumn id="10" xr3:uid="{40F3EA47-8E92-48F7-A24A-6369E84EA096}" name="Теги" dataDxfId="58"/>
+    <tableColumn id="5" xr3:uid="{A1D4F9E4-94BB-4008-834E-B5DC4DE59C40}" name="Дата прийняття" dataDxfId="57"/>
+    <tableColumn id="7" xr3:uid="{2B27F073-AE91-4210-B0D6-642DEFE05F63}" name="Галузь" dataDxfId="56"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3154,7 +3429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B971BF4-F5CF-496D-9610-E7CBA5A28B9C}">
-  <dimension ref="A2:J228"/>
+  <dimension ref="A2:J239"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1"/>
@@ -3343,10 +3618,10 @@
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
@@ -8687,13 +8962,13 @@
       <c r="B222" s="6">
         <v>204</v>
       </c>
-      <c r="C222" s="21" t="s">
+      <c r="C222" s="7" t="s">
         <v>532</v>
       </c>
-      <c r="D222" s="21" t="s">
+      <c r="D222" s="7" t="s">
         <v>533</v>
       </c>
-      <c r="E222" s="21" t="s">
+      <c r="E222" s="7" t="s">
         <v>534</v>
       </c>
       <c r="F222" s="7" t="s">
@@ -8702,23 +8977,23 @@
       <c r="G222" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="H222" s="21"/>
-      <c r="I222" s="23">
+      <c r="H222" s="7"/>
+      <c r="I222" s="14">
         <v>46008</v>
       </c>
-      <c r="J222" s="22"/>
+      <c r="J222" s="15"/>
     </row>
     <row r="223" spans="2:10" ht="240" x14ac:dyDescent="0.25">
       <c r="B223" s="6">
         <v>205</v>
       </c>
-      <c r="C223" s="21" t="s">
+      <c r="C223" s="7" t="s">
         <v>536</v>
       </c>
-      <c r="D223" s="21" t="s">
+      <c r="D223" s="7" t="s">
         <v>535</v>
       </c>
-      <c r="E223" s="21" t="s">
+      <c r="E223" s="7" t="s">
         <v>537</v>
       </c>
       <c r="F223" s="7" t="s">
@@ -8727,23 +9002,23 @@
       <c r="G223" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="H223" s="21"/>
-      <c r="I223" s="23">
+      <c r="H223" s="7"/>
+      <c r="I223" s="14">
         <v>45974</v>
       </c>
-      <c r="J223" s="22"/>
+      <c r="J223" s="15"/>
     </row>
     <row r="224" spans="2:10" ht="270" x14ac:dyDescent="0.25">
       <c r="B224" s="6">
         <v>206</v>
       </c>
-      <c r="C224" s="21" t="s">
+      <c r="C224" s="7" t="s">
         <v>538</v>
       </c>
-      <c r="D224" s="21" t="s">
+      <c r="D224" s="7" t="s">
         <v>539</v>
       </c>
-      <c r="E224" s="21" t="s">
+      <c r="E224" s="7" t="s">
         <v>540</v>
       </c>
       <c r="F224" s="7" t="s">
@@ -8752,23 +9027,23 @@
       <c r="G224" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="H224" s="21"/>
-      <c r="I224" s="23">
+      <c r="H224" s="7"/>
+      <c r="I224" s="14">
         <v>45987</v>
       </c>
-      <c r="J224" s="22"/>
+      <c r="J224" s="15"/>
     </row>
     <row r="225" spans="2:10" ht="165" x14ac:dyDescent="0.25">
       <c r="B225" s="6">
         <v>207</v>
       </c>
-      <c r="C225" s="21" t="s">
+      <c r="C225" s="7" t="s">
         <v>541</v>
       </c>
-      <c r="D225" s="21" t="s">
+      <c r="D225" s="7" t="s">
         <v>542</v>
       </c>
-      <c r="E225" s="21" t="s">
+      <c r="E225" s="7" t="s">
         <v>543</v>
       </c>
       <c r="F225" s="7" t="s">
@@ -8777,80 +9052,353 @@
       <c r="G225" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="H225" s="21"/>
-      <c r="I225" s="23">
+      <c r="H225" s="7"/>
+      <c r="I225" s="14">
         <v>45987</v>
       </c>
-      <c r="J225" s="22"/>
+      <c r="J225" s="15"/>
     </row>
     <row r="226" spans="2:10" ht="105" x14ac:dyDescent="0.25">
       <c r="B226" s="6">
         <v>208</v>
       </c>
-      <c r="C226" s="21" t="s">
+      <c r="C226" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="D226" s="21" t="s">
+      <c r="D226" s="7" t="s">
         <v>547</v>
       </c>
-      <c r="E226" s="21"/>
-      <c r="F226" s="21" t="s">
+      <c r="E226" s="7"/>
+      <c r="F226" s="7" t="s">
         <v>208</v>
       </c>
       <c r="G226" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="H226" s="21"/>
-      <c r="I226" s="23">
+      <c r="H226" s="7"/>
+      <c r="I226" s="14">
         <v>45798</v>
       </c>
-      <c r="J226" s="22"/>
+      <c r="J226" s="15"/>
     </row>
     <row r="227" spans="2:10" ht="120" x14ac:dyDescent="0.25">
       <c r="B227" s="6">
         <v>209</v>
       </c>
-      <c r="C227" s="21" t="s">
+      <c r="C227" s="7" t="s">
         <v>545</v>
       </c>
-      <c r="D227" s="21" t="s">
+      <c r="D227" s="7" t="s">
         <v>546</v>
       </c>
-      <c r="E227" s="21"/>
-      <c r="F227" s="21" t="s">
+      <c r="E227" s="7"/>
+      <c r="F227" s="7" t="s">
         <v>208</v>
       </c>
       <c r="G227" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="H227" s="21"/>
-      <c r="I227" s="23">
+      <c r="H227" s="7"/>
+      <c r="I227" s="14">
         <v>45849</v>
       </c>
-      <c r="J227" s="22"/>
+      <c r="J227" s="15"/>
     </row>
     <row r="228" spans="2:10" ht="195" x14ac:dyDescent="0.25">
       <c r="B228" s="6">
         <v>210</v>
       </c>
-      <c r="C228" s="21" t="s">
+      <c r="C228" s="7" t="s">
         <v>548</v>
       </c>
-      <c r="D228" s="21" t="s">
-        <v>549</v>
-      </c>
-      <c r="E228" s="21"/>
-      <c r="F228" s="21" t="s">
+      <c r="D228" s="7" t="s">
+        <v>551</v>
+      </c>
+      <c r="E228" s="7"/>
+      <c r="F228" s="7" t="s">
         <v>208</v>
       </c>
       <c r="G228" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="H228" s="21"/>
-      <c r="I228" s="23">
+      <c r="H228" s="7"/>
+      <c r="I228" s="14">
         <v>45849</v>
       </c>
-      <c r="J228" s="22"/>
+      <c r="J228" s="15"/>
+    </row>
+    <row r="229" spans="2:10" ht="135" x14ac:dyDescent="0.25">
+      <c r="B229" s="21">
+        <v>211</v>
+      </c>
+      <c r="C229" s="21" t="s">
+        <v>552</v>
+      </c>
+      <c r="D229" s="21" t="s">
+        <v>553</v>
+      </c>
+      <c r="E229" s="21"/>
+      <c r="F229" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G229" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H229" s="21"/>
+      <c r="I229" s="14">
+        <v>46043</v>
+      </c>
+      <c r="J229" s="22"/>
+    </row>
+    <row r="230" spans="2:10" ht="135" x14ac:dyDescent="0.25">
+      <c r="B230" s="6">
+        <v>212</v>
+      </c>
+      <c r="C230" s="21" t="s">
+        <v>554</v>
+      </c>
+      <c r="D230" s="21" t="s">
+        <v>556</v>
+      </c>
+      <c r="E230" s="21" t="s">
+        <v>555</v>
+      </c>
+      <c r="F230" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G230" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H230" s="21"/>
+      <c r="I230" s="14">
+        <v>46052</v>
+      </c>
+      <c r="J230" s="22"/>
+    </row>
+    <row r="231" spans="2:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="B231" s="6">
+        <v>213</v>
+      </c>
+      <c r="C231" s="21" t="s">
+        <v>557</v>
+      </c>
+      <c r="D231" s="21" t="s">
+        <v>559</v>
+      </c>
+      <c r="E231" s="21"/>
+      <c r="F231" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G231" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H231" s="21"/>
+      <c r="I231" s="14">
+        <v>46071</v>
+      </c>
+      <c r="J231" s="22"/>
+    </row>
+    <row r="232" spans="2:10" ht="150" x14ac:dyDescent="0.25">
+      <c r="B232" s="21">
+        <v>214</v>
+      </c>
+      <c r="C232" s="21" t="s">
+        <v>558</v>
+      </c>
+      <c r="D232" s="21" t="s">
+        <v>560</v>
+      </c>
+      <c r="E232" s="21" t="s">
+        <v>570</v>
+      </c>
+      <c r="F232" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G232" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H232" s="21"/>
+      <c r="I232" s="14">
+        <v>46071</v>
+      </c>
+      <c r="J232" s="22"/>
+    </row>
+    <row r="233" spans="2:10" ht="165" x14ac:dyDescent="0.25">
+      <c r="B233" s="6">
+        <v>215</v>
+      </c>
+      <c r="C233" s="21" t="s">
+        <v>562</v>
+      </c>
+      <c r="D233" s="21" t="s">
+        <v>561</v>
+      </c>
+      <c r="E233" s="21" t="s">
+        <v>563</v>
+      </c>
+      <c r="F233" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G233" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H233" s="21"/>
+      <c r="I233" s="14">
+        <v>46076</v>
+      </c>
+      <c r="J233" s="22"/>
+    </row>
+    <row r="234" spans="2:10" ht="225" x14ac:dyDescent="0.25">
+      <c r="B234" s="6">
+        <v>216</v>
+      </c>
+      <c r="C234" s="21" t="s">
+        <v>566</v>
+      </c>
+      <c r="D234" s="21" t="s">
+        <v>564</v>
+      </c>
+      <c r="E234" s="21" t="s">
+        <v>565</v>
+      </c>
+      <c r="F234" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="G234" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H234" s="21"/>
+      <c r="I234" s="23">
+        <v>45681</v>
+      </c>
+      <c r="J234" s="22" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="235" spans="2:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="B235" s="21">
+        <v>217</v>
+      </c>
+      <c r="C235" s="21" t="s">
+        <v>567</v>
+      </c>
+      <c r="D235" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="E235" s="21" t="s">
+        <v>569</v>
+      </c>
+      <c r="F235" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G235" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H235" s="21"/>
+      <c r="I235" s="23">
+        <v>46050</v>
+      </c>
+      <c r="J235" s="22" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="236" spans="2:10" ht="300" x14ac:dyDescent="0.25">
+      <c r="B236" s="21">
+        <v>218</v>
+      </c>
+      <c r="C236" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="D236" s="21" t="s">
+        <v>572</v>
+      </c>
+      <c r="E236" s="21" t="s">
+        <v>574</v>
+      </c>
+      <c r="F236" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G236" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H236" s="21"/>
+      <c r="I236" s="23">
+        <v>46008</v>
+      </c>
+      <c r="J236" s="22"/>
+    </row>
+    <row r="237" spans="2:10" ht="165" x14ac:dyDescent="0.25">
+      <c r="B237" s="21">
+        <v>219</v>
+      </c>
+      <c r="C237" s="21" t="s">
+        <v>575</v>
+      </c>
+      <c r="D237" s="21" t="s">
+        <v>576</v>
+      </c>
+      <c r="E237" s="21"/>
+      <c r="F237" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G237" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H237" s="21"/>
+      <c r="I237" s="23">
+        <v>45874</v>
+      </c>
+      <c r="J237" s="22"/>
+    </row>
+    <row r="238" spans="2:10" ht="180" x14ac:dyDescent="0.25">
+      <c r="B238" s="21">
+        <v>220</v>
+      </c>
+      <c r="C238" s="21" t="s">
+        <v>579</v>
+      </c>
+      <c r="D238" s="21" t="s">
+        <v>578</v>
+      </c>
+      <c r="E238" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="F238" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G238" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H238" s="21"/>
+      <c r="I238" s="23">
+        <v>46010</v>
+      </c>
+      <c r="J238" s="22"/>
+    </row>
+    <row r="239" spans="2:10" ht="165" x14ac:dyDescent="0.25">
+      <c r="B239" s="21">
+        <v>221</v>
+      </c>
+      <c r="C239" s="21" t="s">
+        <v>581</v>
+      </c>
+      <c r="D239" s="21" t="s">
+        <v>580</v>
+      </c>
+      <c r="E239" s="21" t="s">
+        <v>582</v>
+      </c>
+      <c r="F239" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="G239" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H239" s="21"/>
+      <c r="I239" s="23">
+        <v>45826</v>
+      </c>
+      <c r="J239" s="22"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G193:H197">
@@ -8859,31 +9407,31 @@
   <mergeCells count="1">
     <mergeCell ref="C2:H2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G19:G228">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+  <conditionalFormatting sqref="G19:G239">
+    <cfRule type="cellIs" dxfId="35" priority="1" operator="equal">
       <formula>"Невідомо"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="2" operator="equal">
       <formula>"Застосовно (з приміткою)"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="3" operator="equal">
       <formula>"Застосовно"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="4" operator="equal">
       <formula>"Не застосовно"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H10:H12 H14:H15">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="5" operator="equal">
       <formula>"Невідомо"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="6" operator="equal">
       <formula>"Застосовно (з приміткою)"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="7" operator="equal">
       <formula>"Застосовно"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="8" operator="equal">
       <formula>"Не застосовно"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9119,16 +9667,16 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G3:G10">
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="5" operator="equal">
       <formula>"Невідомо"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="6" operator="equal">
       <formula>"Застосовно (з приміткою)"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="7" operator="equal">
       <formula>"Застосовно"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="8" operator="equal">
       <formula>"Не застосовно"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Застосовне законодавство.xlsx
+++ b/Застосовне законодавство.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\x\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\користувач\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B79DD0D-D8B9-4BD0-9F26-ABC3AE3D7A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{37E2801C-5692-49AC-97F1-7FDD9E6B9114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{334805C5-B449-4CB8-AF80-1835CA06DE69}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{334805C5-B449-4CB8-AF80-1835CA06DE69}"/>
   </bookViews>
   <sheets>
     <sheet name="Управління кібербезпекою" sheetId="1" r:id="rId1"/>
@@ -34,8 +34,44 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>користувач</author>
+  </authors>
+  <commentList>
+    <comment ref="B89" authorId="0" shapeId="0" xr:uid="{253938AA-38F3-4ADB-B66A-ABD1D680E198}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>користувач:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+ймовірно замінено на нову постанову, що була восени 2025</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="593">
   <si>
     <t>- В цьому реєстрі перераховані тільки основні законодавчі акти, не враховуючи супутні акти, що затверджують зміни, або покладають завдання з реалізації, наприклад, Національної стратегії кібербезпеки.
 - Сайт ВРУ - основне джерело інформації, оскільки на ньому можна відстежувати актуальність законодавчих актів.</t>
@@ -65,9 +101,6 @@
     <t>https://cip.gov.ua/ua/news/perelik-dokumentiv-normativno-pravovoyi-bazi-sho-zabezpechuye-nadannya-vidpovidnikh-vidiv-poslug-u-galuzi-tekhnichnogo-zakhistu-informaciyi</t>
   </si>
   <si>
-    <t>Не застосовно</t>
-  </si>
-  <si>
     <t>https://cip.gov.ua/ua/news/normativni-dokumenti-sistemi-tzi</t>
   </si>
   <si>
@@ -75,9 +108,6 @@
   </si>
   <si>
     <t>http://altersign.com.ua/korysna-informacija/normatyvna-baza-u-sferi-kzi</t>
-  </si>
-  <si>
-    <t>Застосовно</t>
   </si>
   <si>
     <t>№</t>
@@ -492,9 +522,6 @@
   </si>
   <si>
     <t>https://zakon.rada.gov.ua/laws/show/869-2009-%D0%BF#Text</t>
-  </si>
-  <si>
-    <t>Вимоги до ПЗ, що закуповується або розробляється на замовлення державних органів.</t>
   </si>
   <si>
     <t>Постанова Кабінету Міністрів України від 17липня 2003 року № 1082</t>
@@ -631,9 +658,6 @@
     <t>https://zakon.rada.gov.ua/laws/show/299-2023-%D0%BF#Text</t>
   </si>
   <si>
-    <t>Постанова визначає рекомендації Держспецзв'язку щодо управління інцидентів як обов'язкові для суб'єктів національної системи кібербезпеки.</t>
-  </si>
-  <si>
     <t>Постанова Кабінету Міністрів України від 16.05.2023 № 497 "Про затвердження Порядку пошуку та виявлення потенційної вразливості інформаційних (автоматизованих), електронних комунікаційних, інформаційно-комунікаційних систем, електронних комунікаційних мереж"</t>
   </si>
   <si>
@@ -647,9 +671,6 @@
   </si>
   <si>
     <t>https://cert.gov.ua/recommendation/4256181</t>
-  </si>
-  <si>
-    <t>Вимоги до класифікації інформації про кіберінциденти для обмеження її поширення</t>
   </si>
   <si>
     <t>Протоколи НКЦК</t>
@@ -694,9 +715,6 @@
     <t>Вимоги щодо надання Держспецзв'язком послуг із оцінки стану захищеності ІКС</t>
   </si>
   <si>
-    <t>Накази Адміністрації Держспецзв'язку</t>
-  </si>
-  <si>
     <t>Наказ Адміністрації Держспецзв’язку від 15.01.2016 № 20 «Про затвердження Порядку сканування на предмет вразливості державних інформаційних ресурсів, розміщених в Інтернеті», зареєстрований в Міністерстві юстиції України 05 лютого 2016 року за № 196/28326, Зареєстровано в Міністерстві
 юстиції України
 05 лютого 2016 р.
@@ -754,12 +772,6 @@
     <t>Наказ Адміністрації Держспецзв'язку від 03.07.2023 № 570 «Про затвердження Методичних рекомендацій щодо реагування суб’єктами забезпечення кібербезпеки на різні види подій у кіберпросторі»</t>
   </si>
   <si>
-    <t>https://cip.gov.ua/ua/news/nakaz-administraciyi-derzhspeczv-yazku-vid-03-07-2023-570-pro-zatverdzhennya-metodichnikh-rekomendacii-shodo-reaguvannya-sub-yektami-zabezpechennya-kiberbezpeki-na-rizni-vidi-podii-u-kiberprostori</t>
-  </si>
-  <si>
-    <t>Вимоги до процесу управління інцидентами</t>
-  </si>
-  <si>
     <t>Наказ Адміністрації Держспецзв’язку від 14.07.2023 № 599 «Про затвердження Примірної публічної пропозиції про здійснення пошуку та виявлення потенційної вразливості інформаційних (автоматизованих), електронних комунікаційних, інформаційно-комунікаційних систем, електронних комунікаційних мереж i Методичних рекомендацій з розроблення публічної пропозиції про здійснення пошуку та виявления потенційної вразливості інформаційних (автоматизованих), електронних комунікаційних, інформаційно-комунікаційних систем, електронних комунікаційних мереж»</t>
   </si>
   <si>
@@ -1322,11 +1334,6 @@
 </t>
   </si>
   <si>
-    <t>Положення про забезпечення режиму секретності під 
-час обробки інформації, що становить державну таємницю, в інформаційних, телекомунікаційних та інформаційно-телекомунікаційних системах (для службового 
-користування) - Копію документу можна отримати в режимно-секретному відділі</t>
-  </si>
-  <si>
     <t>Положення визначає порядок утворення та функціонування 
 Реєстру інформаційних, електронних комунікаційних та інформаційно-комунікаційних систем органів виконавчої влади, а також підприємств, установ і організацій, що належать до сфери їх управління</t>
   </si>
@@ -1371,14 +1378,6 @@
   </si>
   <si>
     <t>Наказ Адміністрації Держспецзв’язку від 27.11.2024 № 702 «Про затвердження Методичних рекомендацій щодо проведення незалежного аудиту інформаційної безпеки на об’єктах критичної інфраструктури»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Українська адаптація NIST Cybersecurity Framework 1.1.
-Вимоги щодо критичної інфраструктури (не юстований). 
-Станом на 2025 замість нього є Наказ Адміністрації Держспецзв'язку від 30.01.2025 № 54 </t>
-  </si>
-  <si>
-    <t>NIST Cybersecurity Framework 2.0, адаптований українською.</t>
   </si>
   <si>
     <t>https://www.kmu.gov.ua/npas/deiaki-pytannia-stvorennia-administruvannia-ta-zabezpechennia-funktsionuvannia-zasobu-t210225</t>
@@ -1772,9 +1771,6 @@
     <t>Наказ Адміністрації Держспецзв’язку від 30.01.2026 № 75 «Про затвердження Каталогу заходів з кіберзахисту, базових заходів з кіберзахисту, форми плану кіберзахисту та методичних рекомендацій щодо здійснення заходів з кіберзахисту»</t>
   </si>
   <si>
-    <t>Оновлений переклад NIST CSF 2.0.</t>
-  </si>
-  <si>
     <t>https://cip.gov.ua/ua/news/nakaz-administraciyi-derzhspeczv-yazku-vid-30-01-2026-75-pro-zatverdzhennya-katalogu-zakhodiv-z-kiberzakhistu-bazovikh-zakhodiv-z-kiberzakhistu-formi-planu-kiberzakhistu-ta-metodichnikh-rekomendacii-shodo-zdiisnennya-zakhodiv-z-kiberzakhistu</t>
   </si>
   <si>
@@ -1856,13 +1852,204 @@
   </si>
   <si>
     <t xml:space="preserve">Цей Порядок визначає процедури проведення авторизації з безпеки інформаційних, електронних комунікаційних, інформаційно-комунікаційних, технологічних систем, в яких обробляються державні інформаційні ресурси або інформація з обмеженим доступом, вимога щодо захисту якої встановлена законом, об’єктів критичної інформаційної інфраструктури, власниками або розпорядниками яких є органи державної влади, інші державні органи, державні підприємства, установи та організації, органи місцевого самоврядування (далі - системи), а також підтвердження дотримання вимог з безпеки щодо таких систем протягом їх життєвого циклу. </t>
+  </si>
+  <si>
+    <t>Наказ Адміністрації Держспецзв’язку від 16.04.2026 № 285 «Деякі питання проведення оцінювання стану кіберзахисту»</t>
+  </si>
+  <si>
+    <t>https://cip.gov.ua/ua/news/nakaz-administraciyi-derzhspeczv-yazku-vid-16-04-2026-285-deyaki-pitannya-provedennya-ocinyuvannya-stanu-kiberzakhistu</t>
+  </si>
+  <si>
+    <t>Методичні рекомендації щодо проведення самооцінювання поточного стану кіберзахисту;
+Методичні рекомендації щодо проведення зовнішнього оцінювання
+поточного стану кіберзахисту;
+форму звіту про результати оцінювання стану кіберзахисту;
+Методичні рекомендації щодо складання звіту про результати оцінювання стану кіберзахисту.</t>
+  </si>
+  <si>
+    <t>Наказ Адміністрації Держспецзв’язку від 05.03.2026 № 179 «Про затвердження Порядку ведення репозитарію інформації про кіберінциденти»</t>
+  </si>
+  <si>
+    <t>https://zakon.rada.gov.ua/laws/show/z0473-26#Text</t>
+  </si>
+  <si>
+    <t>Цей Порядок визначає призначення, механізм функціонування та ведення репозитарію інформації про кіберінциденти</t>
+  </si>
+  <si>
+    <t>Так</t>
+  </si>
+  <si>
+    <t>Ні</t>
+  </si>
+  <si>
+    <t>Втратив чинність</t>
+  </si>
+  <si>
+    <t>Положення про забезпечення режиму секретності під 
+час обробки інформації, що становить державну таємницю, в інформаційних, телекомунікаційних та інформаційно-телекомунікаційних системах (для службового користування) - Копію документу можна отримати в режимно-секретному відділі</t>
+  </si>
+  <si>
+    <t>https://zakon.rada.gov.ua/rada/show/v0570519-23#Text</t>
+  </si>
+  <si>
+    <t>Вимоги до розробки</t>
+  </si>
+  <si>
+    <t>Вимоги до Bug Bounty. Втратив чинність (див. Наказ Адміністрації Держспецзв’язку від 18.02.2026 № 141)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Постанова визначає рекомендації Держспецзв'язку щодо управління інцидентів як обов'язкові для суб'єктів національної системи кібербезпеки. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">Втратив чинність. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>Див. Наказ Адміністрації Держспецзв’язку від 18.02.2026 № 143 «Деякі питання реагування на кіберінциденти, кібератаки та кіберзагрози»</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Вимоги до класифікації інформації про кіберінциденти для обмеження її поширення. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>Втратив чинність.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> Див. Наказ Адміністрації Держспецзв’язку від 18.02.2026 № 143 «Деякі питання реагування на кіберінциденти, кібератаки та кіберзагрози»</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Вимоги до процесу управління інцидентами. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">Ймовірно втратив чинність. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>Див. Наказ Адміністрації Держспецзв’язку від 18.02.2026 № 143 «Деякі питання реагування на кіберінциденти, кібератаки та кіберзагрози»</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Українська адаптація NIST Cybersecurity Framework 1.1.
+Вимоги щодо критичної інфраструктури (не юстований). 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>Втратив чинність.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> Див. Наказ Адміністрації Держспецзв’язку від 30.01.2026 № 75 «Про затвердження Каталогу заходів з кіберзахисту, базових заходів з кіберзахисту, форми плану кіберзахисту та методичних рекомендацій щодо здійснення заходів з кіберзахисту»</t>
+    </r>
+  </si>
+  <si>
+    <t>NIST Cybersecurity Framework 2.0, адаптований українською.
+Втратив чинність. Див. Наказ Адміністрації Держспецзв’язку від 30.01.2026 № 75 «Про затвердження Каталогу заходів з кіберзахисту, базових заходів з кіберзахисту, форми плану кіберзахисту та методичних рекомендацій щодо здійснення заходів з кіберзахисту»</t>
+  </si>
+  <si>
+    <t>Оновлений переклад NIST Cybersecurity Framework 2.0.</t>
+  </si>
+  <si>
+    <t>Процедурний документ, не є самобутнім джерелом вимог.</t>
+  </si>
+  <si>
+    <t>Мета обробки даних кіберстатистики – узагальнення та оприлюднення даних кіберстатистики, підготовка звітів для цільової групи користувачів і для оприлюднення.
+Збір та обробка даних кіберстатистики здійснюються Державним центром кіберзахисту Державної служби спеціального зв’язку та захисту інформації України.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Вимоги до ПЗ, що закуповується або розробляється на замовлення державних органів. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>Втратив чинність.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> Див. Постанова Кабінету Міністрів України від 21 лютого 2025 р. № 205 "Деякі питання створення, адміністрування та забезпечення функціонування засобу інформатизації"</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1893,8 +2080,31 @@
       <family val="1"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1904,6 +2114,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9D9D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1961,7 +2195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2021,290 +2255,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="69">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="45">
     <dxf>
       <font>
         <b/>
@@ -3112,21 +3082,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FE4F2F92-58E2-48B9-A7D4-627EBB6ED48E}" name="Таблиця2" displayName="Таблиця2" ref="B18:J239" totalsRowShown="0" headerRowDxfId="68" dataDxfId="66" headerRowBorderDxfId="67" tableBorderDxfId="65">
-  <autoFilter ref="B18:J239" xr:uid="{FE4F2F92-58E2-48B9-A7D4-627EBB6ED48E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FE4F2F92-58E2-48B9-A7D4-627EBB6ED48E}" name="Таблиця2" displayName="Таблиця2" ref="B18:J241" totalsRowShown="0" headerRowDxfId="44" dataDxfId="42" headerRowBorderDxfId="43" tableBorderDxfId="41">
+  <autoFilter ref="B18:J241" xr:uid="{FE4F2F92-58E2-48B9-A7D4-627EBB6ED48E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B19:I200">
     <sortCondition ref="B18:B200"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{DFA9E46C-509D-4A00-A369-7966EED6B176}" name="№" dataDxfId="64"/>
-    <tableColumn id="2" xr3:uid="{981014D8-EFBF-47F5-B054-36010B7987AF}" name="Джерело вимог" dataDxfId="63"/>
-    <tableColumn id="3" xr3:uid="{928FBB84-B24F-469A-AFD2-7EA49120BF89}" name="Посилання" dataDxfId="62"/>
-    <tableColumn id="4" xr3:uid="{D49602E6-E651-4C6D-8A88-C8DCD8A3AFDD}" name="Коментар" dataDxfId="61"/>
-    <tableColumn id="6" xr3:uid="{52AE3B44-6A02-4F51-99B9-C7E17C080BEC}" name="Категорія" dataDxfId="60"/>
-    <tableColumn id="8" xr3:uid="{DE39899F-E232-40DC-A0D1-10B3A973A842}" name="Застосовність" dataDxfId="59"/>
-    <tableColumn id="10" xr3:uid="{40F3EA47-8E92-48F7-A24A-6369E84EA096}" name="Теги" dataDxfId="58"/>
-    <tableColumn id="5" xr3:uid="{A1D4F9E4-94BB-4008-834E-B5DC4DE59C40}" name="Дата прийняття" dataDxfId="57"/>
-    <tableColumn id="7" xr3:uid="{2B27F073-AE91-4210-B0D6-642DEFE05F63}" name="Галузь" dataDxfId="56"/>
+    <tableColumn id="1" xr3:uid="{DFA9E46C-509D-4A00-A369-7966EED6B176}" name="№" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{981014D8-EFBF-47F5-B054-36010B7987AF}" name="Джерело вимог" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{928FBB84-B24F-469A-AFD2-7EA49120BF89}" name="Посилання" dataDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{D49602E6-E651-4C6D-8A88-C8DCD8A3AFDD}" name="Коментар" dataDxfId="37"/>
+    <tableColumn id="6" xr3:uid="{52AE3B44-6A02-4F51-99B9-C7E17C080BEC}" name="Категорія" dataDxfId="36"/>
+    <tableColumn id="8" xr3:uid="{DE39899F-E232-40DC-A0D1-10B3A973A842}" name="Застосовність" dataDxfId="35"/>
+    <tableColumn id="10" xr3:uid="{40F3EA47-8E92-48F7-A24A-6369E84EA096}" name="Теги" dataDxfId="34"/>
+    <tableColumn id="5" xr3:uid="{A1D4F9E4-94BB-4008-834E-B5DC4DE59C40}" name="Дата прийняття" dataDxfId="33"/>
+    <tableColumn id="7" xr3:uid="{2B27F073-AE91-4210-B0D6-642DEFE05F63}" name="Галузь" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3428,24 +3398,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B971BF4-F5CF-496D-9610-E7CBA5A28B9C}">
-  <dimension ref="A2:J239"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B971BF4-F5CF-496D-9610-E7CBA5A28B9C}">
+  <dimension ref="A2:J241"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="1"/>
-    <col min="2" max="2" width="5.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="31.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="48.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="62.140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="34.5703125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.7109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="18.5703125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="19.28515625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="27.140625" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.85546875" style="1"/>
+    <col min="1" max="1" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="5.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="31.5546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="48.109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="62.109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="34.5546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.5546875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="19.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="27.109375" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C2" s="20" t="s">
         <v>0</v>
       </c>
@@ -3455,7 +3425,7 @@
       <c r="G2" s="20"/>
       <c r="H2" s="20"/>
     </row>
-    <row r="3" spans="1:8" ht="13.9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -3514,7 +3484,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
@@ -3526,11 +3496,14 @@
         <v>5</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
+      <c r="H9" s="22" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B10" s="2"/>
@@ -3543,8 +3516,8 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-      <c r="H10" s="3" t="s">
-        <v>9</v>
+      <c r="H10" s="22" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -3553,13 +3526,13 @@
         <v>7</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -3568,13 +3541,13 @@
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="H12" s="3" t="s">
-        <v>13</v>
+      <c r="H12" s="21" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -3583,19 +3556,22 @@
         <v>7</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
+      <c r="H13" s="24" t="s">
+        <v>579</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B14" s="2"/>
       <c r="C14" s="2" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
@@ -3605,10 +3581,10 @@
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="E15" s="2"/>
       <c r="G15" s="2"/>
@@ -3618,10 +3594,10 @@
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2" t="s">
-        <v>550</v>
+        <v>539</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
@@ -3641,31 +3617,31 @@
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
       <c r="B18" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="E18" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="F18" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="G18" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="H18" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>20</v>
-      </c>
       <c r="I18" s="13" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>520</v>
+        <v>509</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="189.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3674,289 +3650,289 @@
         <v>1</v>
       </c>
       <c r="C19" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="F19" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>24</v>
-      </c>
       <c r="G19" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H19" s="6"/>
       <c r="I19" s="12"/>
       <c r="J19" s="12" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="165" x14ac:dyDescent="0.25">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="151.80000000000001" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
       <c r="B20" s="6">
         <v>2</v>
       </c>
       <c r="C20" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="F20" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" s="6" t="s">
         <v>26</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>28</v>
       </c>
       <c r="I20" s="10"/>
       <c r="J20" s="10"/>
     </row>
-    <row r="21" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
       <c r="B21" s="6">
         <v>3</v>
       </c>
       <c r="C21" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>31</v>
-      </c>
       <c r="F21" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H21" s="6"/>
       <c r="I21" s="10"/>
       <c r="J21" s="10"/>
     </row>
-    <row r="22" spans="1:10" ht="165" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="151.80000000000001" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="B22" s="6">
         <v>4</v>
       </c>
       <c r="C22" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>34</v>
-      </c>
       <c r="F22" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H22" s="6"/>
       <c r="I22" s="10"/>
       <c r="J22" s="10"/>
     </row>
-    <row r="23" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="82.8" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" s="6">
         <v>5</v>
       </c>
       <c r="C23" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E23" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="F23" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H23" s="6"/>
       <c r="I23" s="10"/>
       <c r="J23" s="10"/>
     </row>
-    <row r="24" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="124.2" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
       <c r="B24" s="6">
         <v>6</v>
       </c>
       <c r="C24" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>40</v>
-      </c>
       <c r="F24" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H24" s="6"/>
       <c r="I24" s="10"/>
       <c r="J24" s="10"/>
     </row>
-    <row r="25" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="82.8" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
       <c r="B25" s="6">
         <v>7</v>
       </c>
       <c r="C25" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E25" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>43</v>
-      </c>
       <c r="F25" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H25" s="6"/>
       <c r="I25" s="10"/>
       <c r="J25" s="10"/>
     </row>
-    <row r="26" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
       <c r="B26" s="6">
         <v>8</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H26" s="6"/>
       <c r="I26" s="10"/>
       <c r="J26" s="10"/>
     </row>
-    <row r="27" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
       <c r="B27" s="6">
         <v>9</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H27" s="6"/>
       <c r="I27" s="10"/>
       <c r="J27" s="10"/>
     </row>
-    <row r="28" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
       <c r="B28" s="6">
         <v>10</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H28" s="6"/>
       <c r="I28" s="10"/>
       <c r="J28" s="10"/>
     </row>
-    <row r="29" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" s="6">
         <v>11</v>
       </c>
       <c r="C29" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E29" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="F29" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H29" s="6" t="s">
         <v>50</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>52</v>
       </c>
       <c r="I29" s="10"/>
       <c r="J29" s="10"/>
     </row>
-    <row r="30" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
       <c r="B30" s="6">
         <v>12</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H30" s="6"/>
       <c r="I30" s="10"/>
@@ -3968,19 +3944,19 @@
         <v>13</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H31" s="6"/>
       <c r="I31" s="10"/>
@@ -3992,94 +3968,94 @@
         <v>14</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H32" s="6"/>
       <c r="I32" s="10"/>
       <c r="J32" s="10"/>
     </row>
-    <row r="33" spans="1:10" ht="180" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" ht="151.80000000000001" x14ac:dyDescent="0.25">
       <c r="A33" s="4"/>
       <c r="B33" s="6">
         <v>15</v>
       </c>
       <c r="C33" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E33" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D33" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>58</v>
-      </c>
       <c r="F33" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H33" s="6"/>
       <c r="I33" s="10"/>
       <c r="J33" s="10"/>
     </row>
-    <row r="34" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" ht="138" x14ac:dyDescent="0.25">
       <c r="A34" s="4"/>
       <c r="B34" s="6">
         <v>16</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H34" s="6"/>
       <c r="I34" s="10"/>
       <c r="J34" s="10"/>
     </row>
-    <row r="35" spans="1:10" ht="73.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" ht="73.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="6">
         <v>17</v>
       </c>
       <c r="C35" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E35" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="F35" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H35" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>63</v>
       </c>
       <c r="I35" s="10"/>
       <c r="J35" s="10"/>
@@ -4090,314 +4066,314 @@
         <v>18</v>
       </c>
       <c r="C36" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E36" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D36" s="6" t="s">
+      <c r="F36" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E36" s="6" t="s">
+      <c r="G36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>66</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>68</v>
       </c>
       <c r="I36" s="11">
         <v>43013</v>
       </c>
       <c r="J36" s="10"/>
     </row>
-    <row r="37" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="6">
         <v>19</v>
       </c>
       <c r="C37" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E37" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D37" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>71</v>
-      </c>
       <c r="F37" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I37" s="11">
         <v>43272</v>
       </c>
       <c r="J37" s="10"/>
     </row>
-    <row r="38" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" ht="124.2" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="6">
         <v>20</v>
       </c>
       <c r="C38" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E38" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="D38" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>74</v>
-      </c>
       <c r="F38" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I38" s="11">
         <v>38771</v>
       </c>
       <c r="J38" s="10"/>
     </row>
-    <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="6">
         <v>21</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I39" s="11">
         <v>44516</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="6">
         <v>22</v>
       </c>
       <c r="C40" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E40" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="D40" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>79</v>
-      </c>
       <c r="F40" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H40" s="6"/>
       <c r="I40" s="11">
         <v>44181</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="6">
         <v>23</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H41" s="6"/>
       <c r="I41" s="11">
         <v>34520</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="69" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="6">
         <v>24</v>
       </c>
       <c r="C42" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E42" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D42" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>84</v>
-      </c>
       <c r="F42" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H42" s="6"/>
       <c r="I42" s="11">
         <v>43013</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="6">
         <v>25</v>
       </c>
       <c r="C43" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E43" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="D43" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>87</v>
-      </c>
       <c r="F43" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I43" s="11">
         <v>40330</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="6">
         <v>26</v>
       </c>
       <c r="C44" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E44" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="D44" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>90</v>
-      </c>
       <c r="F44" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H44" s="6"/>
       <c r="I44" s="11">
         <v>40556</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="6">
         <v>27</v>
       </c>
       <c r="C45" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E45" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D45" s="6" t="s">
+      <c r="F45" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H45" s="6" t="s">
         <v>92</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="F45" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H45" s="6" t="s">
-        <v>94</v>
       </c>
       <c r="I45" s="11">
         <v>44609</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="82.8" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="6">
         <v>28</v>
       </c>
       <c r="C46" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E46" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D46" s="6" t="s">
+      <c r="F46" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="E46" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>98</v>
-      </c>
       <c r="G46" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I46" s="11">
         <v>44434</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="138" customHeight="1" x14ac:dyDescent="0.25">
@@ -4406,391 +4382,391 @@
         <v>29</v>
       </c>
       <c r="C47" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E47" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="D47" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>101</v>
-      </c>
       <c r="F47" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I47" s="11">
         <v>44593</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="69" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="6">
         <v>30</v>
       </c>
       <c r="C48" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E48" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="D48" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>104</v>
-      </c>
       <c r="F48" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H48" s="6"/>
       <c r="I48" s="11">
         <v>35937</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="210" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="193.2" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="6">
         <v>31</v>
       </c>
       <c r="C49" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E49" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="D49" s="6" t="s">
+      <c r="F49" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H49" s="6" t="s">
         <v>106</v>
-      </c>
-      <c r="E49" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="F49" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H49" s="6" t="s">
-        <v>108</v>
       </c>
       <c r="I49" s="11">
         <v>36430</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="82.8" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="6">
         <v>32</v>
       </c>
       <c r="C50" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E50" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="D50" s="6" t="s">
+      <c r="F50" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="E50" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="F50" s="6" t="s">
-        <v>112</v>
-      </c>
       <c r="G50" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H50" s="6"/>
       <c r="I50" s="11">
         <v>41885</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="69" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="6">
         <v>33</v>
       </c>
       <c r="C51" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="E51" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="D51" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>115</v>
-      </c>
       <c r="F51" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I51" s="11">
         <v>43635</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="6">
         <v>34</v>
       </c>
       <c r="C52" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="E52" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="D52" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>118</v>
-      </c>
       <c r="F52" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I52" s="11">
         <v>44113</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="6">
         <v>35</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I53" s="11">
         <v>44113</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="138" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="6">
         <v>36</v>
       </c>
       <c r="C54" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="E54" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="D54" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>123</v>
-      </c>
       <c r="F54" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I54" s="11">
         <v>44146</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="6">
         <v>37</v>
       </c>
       <c r="C55" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="E55" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="D55" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>126</v>
-      </c>
       <c r="F55" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I55" s="11">
         <v>44188</v>
       </c>
       <c r="J55" s="10"/>
     </row>
-    <row r="56" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" ht="82.8" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="6">
         <v>38</v>
       </c>
       <c r="C56" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="E56" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="D56" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="E56" s="6" t="s">
-        <v>129</v>
-      </c>
       <c r="F56" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I56" s="11">
         <v>45023</v>
       </c>
       <c r="J56" s="10"/>
     </row>
-    <row r="57" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" ht="69" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="6">
         <v>39</v>
       </c>
       <c r="C57" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="E57" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="D57" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>132</v>
-      </c>
       <c r="F57" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I57" s="11">
         <v>44559</v>
       </c>
       <c r="J57" s="10"/>
     </row>
-    <row r="58" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" ht="69" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="6">
         <v>40</v>
       </c>
       <c r="C58" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="E58" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="D58" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>135</v>
-      </c>
       <c r="F58" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H58" s="6"/>
       <c r="I58" s="10" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="J58" s="10"/>
     </row>
-    <row r="59" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="6">
         <v>41</v>
       </c>
       <c r="C59" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="E59" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="D59" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="E59" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="F59" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H59" s="6"/>
       <c r="I59" s="10" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="J59" s="10"/>
     </row>
-    <row r="60" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="6">
         <v>42</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H60" s="6"/>
       <c r="I60" s="11">
@@ -4798,193 +4774,193 @@
       </c>
       <c r="J60" s="10"/>
     </row>
-    <row r="61" spans="1:10" ht="210" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" ht="193.2" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="6">
         <v>43</v>
       </c>
       <c r="C61" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="E61" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="D61" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="E61" s="6" t="s">
-        <v>143</v>
-      </c>
       <c r="F61" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I61" s="11">
         <v>35711</v>
       </c>
       <c r="J61" s="10"/>
     </row>
-    <row r="62" spans="1:10" ht="210" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" ht="193.2" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
-      <c r="B62" s="6">
+      <c r="B62" s="25">
         <v>44</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>146</v>
+        <v>592</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>11</v>
+        <v>110</v>
+      </c>
+      <c r="G62" s="24" t="s">
+        <v>579</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I62" s="11">
         <v>40037</v>
       </c>
       <c r="J62" s="10"/>
     </row>
-    <row r="63" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="6">
         <v>45</v>
       </c>
       <c r="C63" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H63" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="D63" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="E63" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="F63" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H63" s="6" t="s">
-        <v>150</v>
       </c>
       <c r="I63" s="11">
         <v>37819</v>
       </c>
       <c r="J63" s="10"/>
     </row>
-    <row r="64" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="6">
         <v>46</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I64" s="11">
         <v>37819</v>
       </c>
       <c r="J64" s="10"/>
     </row>
-    <row r="65" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="6">
         <v>47</v>
       </c>
       <c r="C65" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H65" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="D65" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="E65" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="F65" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H65" s="6" t="s">
-        <v>156</v>
       </c>
       <c r="I65" s="11">
         <v>37328</v>
       </c>
       <c r="J65" s="10"/>
     </row>
-    <row r="66" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="6">
         <v>48</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I66" s="11">
         <v>41626</v>
       </c>
       <c r="J66" s="10"/>
     </row>
-    <row r="67" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="6">
         <v>49</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H67" s="6"/>
       <c r="I67" s="11">
@@ -4992,53 +4968,53 @@
       </c>
       <c r="J67" s="10"/>
     </row>
-    <row r="68" spans="1:10" ht="210" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" ht="193.2" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
       <c r="B68" s="6">
         <v>50</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I68" s="11">
         <v>42662</v>
       </c>
       <c r="J68" s="10"/>
     </row>
-    <row r="69" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" ht="124.2" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
-      <c r="B69" s="6">
+      <c r="B69" s="25">
         <v>51</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>11</v>
+        <v>110</v>
+      </c>
+      <c r="G69" s="24" t="s">
+        <v>579</v>
       </c>
       <c r="H69" s="6"/>
       <c r="I69" s="11">
@@ -5046,139 +5022,139 @@
       </c>
       <c r="J69" s="10"/>
     </row>
-    <row r="70" spans="1:10" ht="165" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" ht="151.80000000000001" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="6">
         <v>52</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>410</v>
+        <v>580</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I70" s="11">
         <v>35842</v>
       </c>
       <c r="J70" s="10"/>
     </row>
-    <row r="71" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" ht="138" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="6">
         <v>53</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I71" s="11">
         <v>38567</v>
       </c>
       <c r="J71" s="10"/>
     </row>
-    <row r="72" spans="1:10" ht="195" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" ht="179.4" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
       <c r="B72" s="6">
         <v>54</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I72" s="11">
         <v>44188</v>
       </c>
       <c r="J72" s="10"/>
     </row>
-    <row r="73" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" ht="124.2" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="6">
         <v>55</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I73" s="11">
         <v>45044</v>
       </c>
       <c r="J73" s="6" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" ht="345" x14ac:dyDescent="0.25">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="303.60000000000002" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="B74" s="6">
         <v>56</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H74" s="6"/>
       <c r="I74" s="11">
@@ -5186,53 +5162,53 @@
       </c>
       <c r="J74" s="10"/>
     </row>
-    <row r="75" spans="1:10" ht="196.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" ht="196.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="4"/>
-      <c r="B75" s="6">
+      <c r="B75" s="25">
         <v>57</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>188</v>
+        <v>584</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>11</v>
+        <v>110</v>
+      </c>
+      <c r="G75" s="24" t="s">
+        <v>579</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I75" s="11">
         <v>45020</v>
       </c>
       <c r="J75" s="10"/>
     </row>
-    <row r="76" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" ht="138" x14ac:dyDescent="0.25">
       <c r="A76" s="4"/>
       <c r="B76" s="6">
         <v>58</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H76" s="6"/>
       <c r="I76" s="11">
@@ -5240,25 +5216,25 @@
       </c>
       <c r="J76" s="10"/>
     </row>
-    <row r="77" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A77" s="4"/>
-      <c r="B77" s="6">
+      <c r="B77" s="25">
         <v>59</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>194</v>
+        <v>585</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="G77" s="3" t="s">
-        <v>11</v>
+        <v>190</v>
+      </c>
+      <c r="G77" s="24" t="s">
+        <v>579</v>
       </c>
       <c r="H77" s="6"/>
       <c r="I77" s="11">
@@ -5266,278 +5242,278 @@
       </c>
       <c r="J77" s="10"/>
     </row>
-    <row r="78" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
       <c r="A78" s="4"/>
       <c r="B78" s="6">
         <v>60</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I78" s="11">
         <v>44188</v>
       </c>
       <c r="J78" s="10"/>
     </row>
-    <row r="79" spans="1:10" ht="210" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" ht="193.2" x14ac:dyDescent="0.25">
       <c r="A79" s="4"/>
       <c r="B79" s="6">
         <v>61</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I79" s="11">
         <v>39218</v>
       </c>
       <c r="J79" s="10"/>
     </row>
-    <row r="80" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
       <c r="A80" s="4"/>
       <c r="B80" s="6">
         <v>62</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E80" s="6"/>
       <c r="F80" s="6" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I80" s="11">
         <v>42174</v>
       </c>
       <c r="J80" s="10"/>
     </row>
-    <row r="81" spans="1:10" ht="240" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" ht="207" x14ac:dyDescent="0.25">
       <c r="A81" s="4"/>
       <c r="B81" s="6">
         <v>63</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I81" s="11">
         <v>41975</v>
       </c>
       <c r="J81" s="10"/>
     </row>
-    <row r="82" spans="1:10" ht="210" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" ht="193.2" x14ac:dyDescent="0.25">
       <c r="A82" s="4"/>
       <c r="B82" s="6">
         <v>64</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I82" s="11">
         <v>42384</v>
       </c>
       <c r="J82" s="10"/>
     </row>
-    <row r="83" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" ht="82.8" x14ac:dyDescent="0.25">
       <c r="A83" s="4"/>
       <c r="B83" s="6">
         <v>65</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I83" s="11">
         <v>44211</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" ht="255" x14ac:dyDescent="0.25">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="234.6" x14ac:dyDescent="0.25">
       <c r="A84" s="4"/>
       <c r="B84" s="6">
         <v>66</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I84" s="11">
         <v>44449</v>
       </c>
       <c r="J84" s="6" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
       <c r="B85" s="6">
         <v>67</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>426</v>
+        <v>587</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="G85" s="3" t="s">
-        <v>11</v>
+        <v>197</v>
+      </c>
+      <c r="G85" s="24" t="s">
+        <v>579</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I85" s="11">
         <v>44475</v>
       </c>
       <c r="J85" s="6" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" ht="225" x14ac:dyDescent="0.25">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="207" x14ac:dyDescent="0.25">
       <c r="B86" s="6">
         <v>68</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I86" s="11">
         <v>44736</v>
       </c>
       <c r="J86" s="10"/>
     </row>
-    <row r="87" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
       <c r="B87" s="6">
         <v>69</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H87" s="6"/>
       <c r="I87" s="11">
@@ -5545,51 +5521,51 @@
       </c>
       <c r="J87" s="10"/>
     </row>
-    <row r="88" spans="1:10" ht="105" x14ac:dyDescent="0.25">
-      <c r="B88" s="6">
+    <row r="88" spans="1:10" ht="96.6" x14ac:dyDescent="0.25">
+      <c r="B88" s="25">
         <v>70</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="D88" s="6" t="s">
-        <v>225</v>
+        <v>218</v>
+      </c>
+      <c r="D88" s="23" t="s">
+        <v>581</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>226</v>
+        <v>586</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I88" s="11">
         <v>45110</v>
       </c>
       <c r="J88" s="10"/>
     </row>
-    <row r="89" spans="1:10" ht="330" x14ac:dyDescent="0.25">
-      <c r="B89" s="6">
+    <row r="89" spans="1:10" ht="289.8" x14ac:dyDescent="0.25">
+      <c r="B89" s="25">
         <v>71</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>191</v>
+        <v>583</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>11</v>
+        <v>197</v>
+      </c>
+      <c r="G89" s="24" t="s">
+        <v>579</v>
       </c>
       <c r="H89" s="6"/>
       <c r="I89" s="11">
@@ -5597,24 +5573,24 @@
       </c>
       <c r="J89" s="10"/>
     </row>
-    <row r="90" spans="1:10" ht="195" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" ht="179.4" x14ac:dyDescent="0.25">
       <c r="B90" s="6">
         <v>72</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H90" s="6"/>
       <c r="I90" s="11">
@@ -5622,24 +5598,24 @@
       </c>
       <c r="J90" s="10"/>
     </row>
-    <row r="91" spans="1:10" ht="240" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" ht="220.8" x14ac:dyDescent="0.25">
       <c r="B91" s="6">
         <v>73</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H91" s="6"/>
       <c r="I91" s="11">
@@ -5647,283 +5623,283 @@
       </c>
       <c r="J91" s="10"/>
     </row>
-    <row r="92" spans="1:10" ht="315" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" ht="289.8" x14ac:dyDescent="0.25">
       <c r="B92" s="6">
         <v>74</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I92" s="11">
         <v>39609</v>
       </c>
       <c r="J92" s="10"/>
     </row>
-    <row r="93" spans="1:10" ht="210" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B93" s="6">
         <v>75</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I93" s="11">
         <v>35065</v>
       </c>
       <c r="J93" s="10"/>
     </row>
-    <row r="94" spans="1:10" ht="210" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B94" s="6">
         <v>76</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I94" s="11">
         <v>35065</v>
       </c>
       <c r="J94" s="10"/>
     </row>
-    <row r="95" spans="1:10" ht="210" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B95" s="6">
         <v>77</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I95" s="11">
         <v>35431</v>
       </c>
       <c r="J95" s="10"/>
     </row>
-    <row r="96" spans="1:10" ht="210" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B96" s="6">
         <v>78</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E96" s="7"/>
       <c r="F96" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I96" s="11">
         <v>36161</v>
       </c>
       <c r="J96" s="10"/>
     </row>
-    <row r="97" spans="1:10" ht="210" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" ht="193.2" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="B97" s="6">
         <v>79</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="D97" s="7" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="E97" s="7"/>
       <c r="F97" s="7" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H97" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I97" s="11">
         <v>36161</v>
       </c>
       <c r="J97" s="10"/>
     </row>
-    <row r="98" spans="1:10" ht="210" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B98" s="6">
         <v>80</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="E98" s="6"/>
       <c r="F98" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I98" s="11">
         <v>36526</v>
       </c>
       <c r="J98" s="10"/>
     </row>
-    <row r="99" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" ht="96.6" x14ac:dyDescent="0.25">
       <c r="B99" s="6">
         <v>81</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="E99" s="6"/>
       <c r="F99" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H99" s="6" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="I99" s="11">
         <v>39448</v>
       </c>
       <c r="J99" s="10"/>
     </row>
-    <row r="100" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B100" s="6">
         <v>82</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="E100" s="6"/>
       <c r="F100" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="I100" s="11">
         <v>36526</v>
       </c>
       <c r="J100" s="10"/>
     </row>
-    <row r="101" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" ht="69" x14ac:dyDescent="0.25">
       <c r="B101" s="6">
         <v>83</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E101" s="6"/>
       <c r="F101" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="I101" s="11">
         <v>40909</v>
       </c>
       <c r="J101" s="10"/>
     </row>
-    <row r="102" spans="1:10" ht="180" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" ht="165.6" x14ac:dyDescent="0.25">
       <c r="B102" s="6">
         <v>84</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="E102" s="6"/>
       <c r="F102" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H102" s="6" t="str">
         <f>"#ТЗІ"</f>
@@ -5934,197 +5910,197 @@
       </c>
       <c r="J102" s="10"/>
     </row>
-    <row r="103" spans="1:10" ht="210" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B103" s="6">
         <v>85</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="D103" s="6"/>
       <c r="E103" s="6" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="F103" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H103" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I103" s="11">
         <v>37987</v>
       </c>
       <c r="J103" s="10"/>
     </row>
-    <row r="104" spans="1:10" ht="210" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B104" s="6">
         <v>86</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="E104" s="6"/>
       <c r="F104" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I104" s="11">
         <v>41275</v>
       </c>
       <c r="J104" s="10"/>
     </row>
-    <row r="105" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
       <c r="B105" s="6">
         <v>87</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="D105" s="6"/>
       <c r="E105" s="6" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I105" s="11">
         <v>42005</v>
       </c>
       <c r="J105" s="10"/>
     </row>
-    <row r="106" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
       <c r="B106" s="6">
         <v>88</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="D106" s="6"/>
       <c r="E106" s="6" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I106" s="11">
         <v>42005</v>
       </c>
       <c r="J106" s="10"/>
     </row>
-    <row r="107" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
       <c r="B107" s="6">
         <v>89</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="D107" s="6"/>
       <c r="E107" s="6" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H107" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I107" s="11">
         <v>42005</v>
       </c>
       <c r="J107" s="10"/>
     </row>
-    <row r="108" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
       <c r="B108" s="6">
         <v>90</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="D108" s="6"/>
       <c r="E108" s="6" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I108" s="11">
         <v>42005</v>
       </c>
       <c r="J108" s="10"/>
     </row>
-    <row r="109" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" ht="69" x14ac:dyDescent="0.25">
       <c r="B109" s="6">
         <v>91</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="E109" s="6"/>
       <c r="F109" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="I109" s="11">
         <v>36892</v>
       </c>
       <c r="J109" s="10"/>
     </row>
-    <row r="110" spans="1:10" ht="165" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" ht="138" x14ac:dyDescent="0.25">
       <c r="B110" s="6">
         <v>92</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="E110" s="6"/>
       <c r="F110" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H110" s="6" t="str">
         <f>"#ТЗІ"</f>
@@ -6135,22 +6111,22 @@
       </c>
       <c r="J110" s="10"/>
     </row>
-    <row r="111" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" ht="138" x14ac:dyDescent="0.25">
       <c r="B111" s="6">
         <v>93</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E111" s="6"/>
       <c r="F111" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H111" s="6" t="str">
         <f>"#ТЗІ"</f>
@@ -6161,200 +6137,200 @@
       </c>
       <c r="J111" s="10"/>
     </row>
-    <row r="112" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" ht="69" x14ac:dyDescent="0.25">
       <c r="B112" s="6">
         <v>94</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="E112" s="6"/>
       <c r="F112" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="I112" s="11">
         <v>36892</v>
       </c>
       <c r="J112" s="10"/>
     </row>
-    <row r="113" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B113" s="6">
         <v>95</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="D113" s="6"/>
       <c r="E113" s="6" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H113" s="6" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="I113" s="11">
         <v>36892</v>
       </c>
       <c r="J113" s="10"/>
     </row>
-    <row r="114" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" ht="69" x14ac:dyDescent="0.25">
       <c r="B114" s="6">
         <v>96</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="E114" s="6"/>
       <c r="F114" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="I114" s="11">
         <v>36892</v>
       </c>
       <c r="J114" s="10"/>
     </row>
-    <row r="115" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
       <c r="B115" s="6">
         <v>97</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="D115" s="6"/>
       <c r="E115" s="6" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H115" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I115" s="11">
         <v>42005</v>
       </c>
       <c r="J115" s="10"/>
     </row>
-    <row r="116" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
       <c r="B116" s="6">
         <v>98</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="D116" s="6"/>
       <c r="E116" s="6" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I116" s="11">
         <v>42005</v>
       </c>
       <c r="J116" s="10"/>
     </row>
-    <row r="117" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
       <c r="B117" s="6">
         <v>99</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="D117" s="6"/>
       <c r="E117" s="6" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H117" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I117" s="11">
         <v>42005</v>
       </c>
       <c r="J117" s="10"/>
     </row>
-    <row r="118" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
       <c r="B118" s="6">
         <v>100</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="D118" s="6"/>
       <c r="E118" s="6" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I118" s="11">
         <v>42005</v>
       </c>
       <c r="J118" s="10"/>
     </row>
-    <row r="119" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" ht="82.8" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="B119" s="6">
         <v>101</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="E119" s="6"/>
       <c r="F119" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H119" s="6" t="str">
         <f>"#ТЗІ"</f>
@@ -6365,22 +6341,22 @@
       </c>
       <c r="J119" s="10"/>
     </row>
-    <row r="120" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B120" s="6">
         <v>102</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="E120" s="6"/>
       <c r="F120" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H120" s="6" t="str">
         <f>"#ТЗІ"</f>
@@ -6391,22 +6367,22 @@
       </c>
       <c r="J120" s="10"/>
     </row>
-    <row r="121" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B121" s="6">
         <v>103</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="E121" s="6"/>
       <c r="F121" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H121" s="6" t="str">
         <f>"#ТЗІ"</f>
@@ -6417,272 +6393,272 @@
       </c>
       <c r="J121" s="10"/>
     </row>
-    <row r="122" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
       <c r="B122" s="6">
         <v>104</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="D122" s="6"/>
       <c r="E122" s="6" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I122" s="11">
         <v>42005</v>
       </c>
       <c r="J122" s="10"/>
     </row>
-    <row r="123" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
       <c r="B123" s="6">
         <v>105</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="D123" s="6"/>
       <c r="E123" s="6" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H123" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I123" s="11">
         <v>42005</v>
       </c>
       <c r="J123" s="10"/>
     </row>
-    <row r="124" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
       <c r="B124" s="6">
         <v>106</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="D124" s="6"/>
       <c r="E124" s="6" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I124" s="11">
         <v>42005</v>
       </c>
       <c r="J124" s="10"/>
     </row>
-    <row r="125" spans="1:10" ht="210" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B125" s="6">
         <v>107</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="E125" s="6"/>
       <c r="F125" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H125" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I125" s="11">
         <v>36161</v>
       </c>
       <c r="J125" s="10"/>
     </row>
-    <row r="126" spans="1:10" ht="210" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B126" s="6">
         <v>108</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E126" s="6"/>
       <c r="F126" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I126" s="11">
         <v>36161</v>
       </c>
       <c r="J126" s="10"/>
     </row>
-    <row r="127" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
       <c r="B127" s="6">
         <v>109</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="E127" s="6"/>
       <c r="F127" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H127" s="6" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="I127" s="11">
         <v>36161</v>
       </c>
       <c r="J127" s="10"/>
     </row>
-    <row r="128" spans="1:10" ht="210" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B128" s="6">
         <v>110</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="E128" s="6"/>
       <c r="F128" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I128" s="11">
         <v>37257</v>
       </c>
       <c r="J128" s="10"/>
     </row>
-    <row r="129" spans="2:10" ht="210" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:10" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B129" s="6">
         <v>111</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="E129" s="6"/>
       <c r="F129" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H129" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I129" s="11">
         <v>37622</v>
       </c>
       <c r="J129" s="10"/>
     </row>
-    <row r="130" spans="2:10" ht="120" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:10" ht="110.4" x14ac:dyDescent="0.25">
       <c r="B130" s="6">
         <v>112</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="D130" s="6"/>
       <c r="E130" s="6" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="F130" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I130" s="11">
         <v>42005</v>
       </c>
       <c r="J130" s="10"/>
     </row>
-    <row r="131" spans="2:10" ht="210" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:10" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B131" s="6">
         <v>113</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="E131" s="6"/>
       <c r="F131" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H131" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I131" s="11">
         <v>40544</v>
       </c>
       <c r="J131" s="10"/>
     </row>
-    <row r="132" spans="2:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B132" s="6">
         <v>114</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="E132" s="6"/>
       <c r="F132" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H132" s="6" t="str">
         <f>"#ТЗІ"</f>
@@ -6693,195 +6669,195 @@
       </c>
       <c r="J132" s="10"/>
     </row>
-    <row r="133" spans="2:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:10" ht="69" x14ac:dyDescent="0.25">
       <c r="B133" s="6">
         <v>115</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="E133" s="6"/>
       <c r="F133" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H133" s="6" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="I133" s="11">
         <v>36161</v>
       </c>
       <c r="J133" s="10"/>
     </row>
-    <row r="134" spans="2:10" ht="210" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:10" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B134" s="6">
         <v>116</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="E134" s="6"/>
       <c r="F134" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I134" s="11">
         <v>39814</v>
       </c>
       <c r="J134" s="10"/>
     </row>
-    <row r="135" spans="2:10" ht="210" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:10" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B135" s="6">
         <v>117</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="E135" s="6"/>
       <c r="F135" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H135" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I135" s="11">
         <v>39814</v>
       </c>
       <c r="J135" s="10"/>
     </row>
-    <row r="136" spans="2:10" ht="120" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:10" ht="110.4" x14ac:dyDescent="0.25">
       <c r="B136" s="6">
         <v>118</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="E136" s="6"/>
       <c r="F136" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="I136" s="11">
         <v>40909</v>
       </c>
       <c r="J136" s="10"/>
     </row>
-    <row r="137" spans="2:10" ht="120" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:10" ht="110.4" x14ac:dyDescent="0.25">
       <c r="B137" s="6">
         <v>119</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="D137" s="6"/>
       <c r="E137" s="6" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="F137" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H137" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I137" s="11">
         <v>42005</v>
       </c>
       <c r="J137" s="10"/>
     </row>
-    <row r="138" spans="2:10" ht="210" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:10" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B138" s="6">
         <v>120</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="D138" s="6"/>
       <c r="E138" s="6"/>
       <c r="F138" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I138" s="11">
         <v>36526</v>
       </c>
       <c r="J138" s="10"/>
     </row>
-    <row r="139" spans="2:10" ht="210" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:10" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B139" s="6">
         <v>121</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="D139" s="6"/>
       <c r="E139" s="6" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="F139" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H139" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I139" s="11">
         <v>42370</v>
       </c>
       <c r="J139" s="10"/>
     </row>
-    <row r="140" spans="2:10" ht="135" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:10" ht="124.2" x14ac:dyDescent="0.25">
       <c r="B140" s="6">
         <v>122</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="E140" s="6"/>
       <c r="F140" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H140" s="6" t="str">
         <f t="shared" ref="H140:H145" si="0">"#ТЗІ"</f>
@@ -6892,22 +6868,22 @@
       </c>
       <c r="J140" s="10"/>
     </row>
-    <row r="141" spans="2:10" ht="180" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:10" ht="165.6" x14ac:dyDescent="0.25">
       <c r="B141" s="6">
         <v>123</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="E141" s="6"/>
       <c r="F141" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H141" s="6" t="str">
         <f t="shared" si="0"/>
@@ -6918,22 +6894,22 @@
       </c>
       <c r="J141" s="10"/>
     </row>
-    <row r="142" spans="2:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:10" ht="55.2" x14ac:dyDescent="0.25">
       <c r="B142" s="6">
         <v>124</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="E142" s="6"/>
       <c r="F142" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H142" s="6" t="str">
         <f t="shared" si="0"/>
@@ -6944,22 +6920,22 @@
       </c>
       <c r="J142" s="10"/>
     </row>
-    <row r="143" spans="2:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:10" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B143" s="6">
         <v>125</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E143" s="6"/>
       <c r="F143" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H143" s="6" t="str">
         <f t="shared" si="0"/>
@@ -6970,22 +6946,22 @@
       </c>
       <c r="J143" s="10"/>
     </row>
-    <row r="144" spans="2:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:10" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B144" s="6">
         <v>126</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="E144" s="6"/>
       <c r="F144" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G144" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H144" s="6" t="str">
         <f t="shared" si="0"/>
@@ -6996,22 +6972,22 @@
       </c>
       <c r="J144" s="10"/>
     </row>
-    <row r="145" spans="2:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B145" s="6">
         <v>127</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="E145" s="6"/>
       <c r="F145" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G145" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H145" s="6" t="str">
         <f t="shared" si="0"/>
@@ -7022,72 +6998,72 @@
       </c>
       <c r="J145" s="10"/>
     </row>
-    <row r="146" spans="2:10" ht="210" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:10" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B146" s="6">
         <v>128</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="E146" s="6"/>
       <c r="F146" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I146" s="11">
         <v>36161</v>
       </c>
       <c r="J146" s="10"/>
     </row>
-    <row r="147" spans="2:10" ht="210" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:10" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B147" s="6">
         <v>129</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="E147" s="6"/>
       <c r="F147" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H147" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I147" s="11">
         <v>44927</v>
       </c>
       <c r="J147" s="10"/>
     </row>
-    <row r="148" spans="2:10" ht="165" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:10" ht="151.80000000000001" x14ac:dyDescent="0.25">
       <c r="B148" s="6">
         <v>130</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="E148" s="6"/>
       <c r="F148" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H148" s="6" t="str">
         <f>"#ТЗІ"</f>
@@ -7098,131 +7074,131 @@
       </c>
       <c r="J148" s="10"/>
     </row>
-    <row r="149" spans="2:10" ht="120" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:10" ht="96.6" x14ac:dyDescent="0.25">
       <c r="B149" s="6">
         <v>131</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="E149" s="6"/>
       <c r="F149" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H149" s="6" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="I149" s="11">
         <v>36526</v>
       </c>
       <c r="J149" s="10"/>
     </row>
-    <row r="150" spans="2:10" ht="195" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:10" ht="179.4" x14ac:dyDescent="0.25">
       <c r="B150" s="6">
         <v>132</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="E150" s="6"/>
       <c r="F150" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="I150" s="11">
         <v>34700</v>
       </c>
       <c r="J150" s="10"/>
     </row>
-    <row r="151" spans="2:10" ht="165" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:10" ht="151.80000000000001" x14ac:dyDescent="0.25">
       <c r="B151" s="6">
         <v>133</v>
       </c>
       <c r="C151" s="7" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="D151" s="7" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="E151" s="7"/>
       <c r="F151" s="7" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H151" s="7" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="I151" s="11">
         <v>34700</v>
       </c>
       <c r="J151" s="10"/>
     </row>
-    <row r="152" spans="2:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:10" ht="55.2" x14ac:dyDescent="0.25">
       <c r="B152" s="6">
         <v>134</v>
       </c>
       <c r="C152" s="7" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="D152" s="7" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="E152" s="7"/>
-      <c r="F152" s="7" t="s">
-        <v>202</v>
+      <c r="F152" s="6" t="s">
+        <v>197</v>
       </c>
       <c r="G152" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H152" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I152" s="11">
         <v>45467</v>
       </c>
       <c r="J152" s="10"/>
     </row>
-    <row r="153" spans="2:10" ht="120" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:10" ht="96.6" x14ac:dyDescent="0.25">
       <c r="B153" s="6">
         <v>135</v>
       </c>
       <c r="C153" s="7" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="D153" s="7" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E153" s="7"/>
-      <c r="F153" s="7" t="s">
-        <v>202</v>
+      <c r="F153" s="6" t="s">
+        <v>197</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H153" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I153" s="11">
         <v>45412</v>
       </c>
       <c r="J153" s="6" t="s">
-        <v>522</v>
+        <v>511</v>
       </c>
     </row>
     <row r="154" spans="2:10" x14ac:dyDescent="0.25">
@@ -7230,23 +7206,23 @@
         <v>136</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="E154" s="6"/>
       <c r="F154" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I154" s="11">
         <v>43466</v>
       </c>
       <c r="J154" s="10" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="155" spans="2:10" x14ac:dyDescent="0.25">
@@ -7254,23 +7230,23 @@
         <v>137</v>
       </c>
       <c r="C155" s="9" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="E155" s="6"/>
       <c r="F155" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="G155" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H155" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I155" s="11">
         <v>43466</v>
       </c>
       <c r="J155" s="10" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="156" spans="2:10" x14ac:dyDescent="0.25">
@@ -7278,23 +7254,23 @@
         <v>138</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="E156" s="6"/>
       <c r="F156" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I156" s="11">
         <v>42736</v>
       </c>
       <c r="J156" s="10" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="157" spans="2:10" x14ac:dyDescent="0.25">
@@ -7302,23 +7278,23 @@
         <v>139</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="E157" s="6"/>
       <c r="F157" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H157" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I157" s="11">
         <v>42736</v>
       </c>
       <c r="J157" s="10" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="158" spans="2:10" x14ac:dyDescent="0.25">
@@ -7326,23 +7302,23 @@
         <v>140</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="E158" s="6"/>
       <c r="F158" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H158" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I158" s="11">
         <v>43466</v>
       </c>
       <c r="J158" s="10" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="159" spans="2:10" x14ac:dyDescent="0.25">
@@ -7350,23 +7326,23 @@
         <v>141</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="E159" s="6"/>
       <c r="F159" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H159" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I159" s="11">
         <v>43466</v>
       </c>
       <c r="J159" s="10" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="160" spans="2:10" x14ac:dyDescent="0.25">
@@ -7374,23 +7350,23 @@
         <v>142</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="E160" s="6"/>
       <c r="F160" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I160" s="11">
         <v>44197</v>
       </c>
       <c r="J160" s="10" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="161" spans="2:10" x14ac:dyDescent="0.25">
@@ -7398,23 +7374,23 @@
         <v>143</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="E161" s="6"/>
       <c r="F161" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H161" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I161" s="11" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="J161" s="10" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="162" spans="2:10" x14ac:dyDescent="0.25">
@@ -7422,26 +7398,26 @@
         <v>144</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="E162" s="6"/>
       <c r="F162" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H162" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I162" s="11">
         <v>40179</v>
       </c>
       <c r="J162" s="10" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="163" spans="2:10" x14ac:dyDescent="0.25">
@@ -7449,23 +7425,23 @@
         <v>145</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="E163" s="6"/>
       <c r="F163" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H163" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I163" s="11">
         <v>41640</v>
       </c>
       <c r="J163" s="10" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="164" spans="2:10" x14ac:dyDescent="0.25">
@@ -7473,23 +7449,23 @@
         <v>146</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="E164" s="6"/>
       <c r="F164" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H164" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I164" s="11">
         <v>42005</v>
       </c>
       <c r="J164" s="10" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="165" spans="2:10" x14ac:dyDescent="0.25">
@@ -7497,23 +7473,23 @@
         <v>147</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="E165" s="6"/>
       <c r="F165" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H165" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I165" s="11">
         <v>42005</v>
       </c>
       <c r="J165" s="10" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="166" spans="2:10" x14ac:dyDescent="0.25">
@@ -7521,26 +7497,26 @@
         <v>148</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="E166" s="6"/>
       <c r="F166" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H166" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I166" s="11">
         <v>36526</v>
       </c>
       <c r="J166" s="10" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="167" spans="2:10" x14ac:dyDescent="0.25">
@@ -7548,26 +7524,26 @@
         <v>149</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="E167" s="6"/>
       <c r="F167" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H167" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I167" s="11">
         <v>36526</v>
       </c>
       <c r="J167" s="10" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="168" spans="2:10" x14ac:dyDescent="0.25">
@@ -7575,26 +7551,26 @@
         <v>150</v>
       </c>
       <c r="C168" s="9" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="E168" s="6"/>
       <c r="F168" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H168" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I168" s="11">
         <v>36892</v>
       </c>
       <c r="J168" s="10" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="169" spans="2:10" x14ac:dyDescent="0.25">
@@ -7602,26 +7578,26 @@
         <v>151</v>
       </c>
       <c r="C169" s="9" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="E169" s="6"/>
       <c r="F169" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="G169" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H169" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I169" s="11">
         <v>36892</v>
       </c>
       <c r="J169" s="10" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="170" spans="2:10" x14ac:dyDescent="0.25">
@@ -7629,26 +7605,26 @@
         <v>152</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="E170" s="6"/>
       <c r="F170" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H170" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I170" s="11">
         <v>37257</v>
       </c>
       <c r="J170" s="10" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="171" spans="2:10" x14ac:dyDescent="0.25">
@@ -7656,26 +7632,26 @@
         <v>153</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="E171" s="6"/>
       <c r="F171" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="G171" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H171" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I171" s="11">
         <v>37257</v>
       </c>
       <c r="J171" s="10" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="172" spans="2:10" x14ac:dyDescent="0.25">
@@ -7683,26 +7659,26 @@
         <v>154</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="E172" s="7"/>
       <c r="F172" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="G172" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H172" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I172" s="11">
         <v>37622</v>
       </c>
       <c r="J172" s="10" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="173" spans="2:10" x14ac:dyDescent="0.25">
@@ -7710,26 +7686,26 @@
         <v>155</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="E173" s="6"/>
       <c r="F173" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="G173" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H173" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I173" s="11">
         <v>37987</v>
       </c>
       <c r="J173" s="10" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="174" spans="2:10" x14ac:dyDescent="0.25">
@@ -7737,26 +7713,26 @@
         <v>156</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="E174" s="6"/>
       <c r="F174" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H174" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I174" s="11">
         <v>38353</v>
       </c>
       <c r="J174" s="10" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="175" spans="2:10" x14ac:dyDescent="0.25">
@@ -7764,23 +7740,23 @@
         <v>157</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="E175" s="6"/>
       <c r="F175" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H175" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I175" s="11">
         <v>38718</v>
       </c>
       <c r="J175" s="10" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="176" spans="2:10" x14ac:dyDescent="0.25">
@@ -7788,23 +7764,23 @@
         <v>158</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="E176" s="6"/>
       <c r="F176" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H176" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I176" s="11">
         <v>42005</v>
       </c>
       <c r="J176" s="10" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="177" spans="2:10" x14ac:dyDescent="0.25">
@@ -7812,26 +7788,26 @@
         <v>159</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="E177" s="6"/>
       <c r="F177" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="G177" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H177" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I177" s="11">
         <v>44562</v>
       </c>
       <c r="J177" s="10" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="178" spans="2:10" x14ac:dyDescent="0.25">
@@ -7839,23 +7815,23 @@
         <v>160</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="E178" s="6"/>
       <c r="F178" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="G178" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H178" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I178" s="11">
         <v>44197</v>
       </c>
       <c r="J178" s="10" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="179" spans="2:10" x14ac:dyDescent="0.25">
@@ -7863,26 +7839,26 @@
         <v>161</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="E179" s="6"/>
       <c r="F179" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H179" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I179" s="11">
         <v>37257</v>
       </c>
       <c r="J179" s="10" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="180" spans="2:10" x14ac:dyDescent="0.25">
@@ -7890,26 +7866,26 @@
         <v>162</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="E180" s="6"/>
       <c r="F180" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H180" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I180" s="11">
         <v>37257</v>
       </c>
       <c r="J180" s="10" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="181" spans="2:10" x14ac:dyDescent="0.25">
@@ -7917,26 +7893,26 @@
         <v>163</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="E181" s="6"/>
       <c r="F181" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H181" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I181" s="11">
         <v>39083</v>
       </c>
       <c r="J181" s="10" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="182" spans="2:10" x14ac:dyDescent="0.25">
@@ -7944,23 +7920,23 @@
         <v>164</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="E182" s="6"/>
       <c r="F182" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="G182" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H182" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I182" s="11">
         <v>39448</v>
       </c>
       <c r="J182" s="10" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="183" spans="2:10" x14ac:dyDescent="0.25">
@@ -7968,23 +7944,23 @@
         <v>165</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="E183" s="6"/>
       <c r="F183" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="G183" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H183" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I183" s="11">
         <v>42005</v>
       </c>
       <c r="J183" s="10" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="184" spans="2:10" x14ac:dyDescent="0.25">
@@ -7992,23 +7968,23 @@
         <v>166</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="E184" s="6"/>
       <c r="F184" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="G184" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H184" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I184" s="11">
         <v>44197</v>
       </c>
       <c r="J184" s="10" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="185" spans="2:10" x14ac:dyDescent="0.25">
@@ -8016,23 +7992,23 @@
         <v>167</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="E185" s="6"/>
       <c r="F185" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="G185" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H185" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I185" s="11">
         <v>44562</v>
       </c>
       <c r="J185" s="10" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="186" spans="2:10" x14ac:dyDescent="0.25">
@@ -8040,23 +8016,23 @@
         <v>168</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="E186" s="6"/>
       <c r="F186" s="6" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H186" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I186" s="11">
         <v>44197</v>
       </c>
       <c r="J186" s="10" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="187" spans="2:10" x14ac:dyDescent="0.25">
@@ -8064,23 +8040,23 @@
         <v>169</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="E187" s="6"/>
       <c r="F187" s="6" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H187" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I187" s="11">
         <v>44197</v>
       </c>
       <c r="J187" s="10" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="188" spans="2:10" x14ac:dyDescent="0.25">
@@ -8088,23 +8064,23 @@
         <v>170</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="E188" s="6"/>
       <c r="F188" s="6" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H188" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I188" s="11">
         <v>44197</v>
       </c>
       <c r="J188" s="10" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="189" spans="2:10" x14ac:dyDescent="0.25">
@@ -8112,23 +8088,23 @@
         <v>171</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="E189" s="6"/>
       <c r="F189" s="6" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H189" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I189" s="11">
         <v>44197</v>
       </c>
       <c r="J189" s="10" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="190" spans="2:10" x14ac:dyDescent="0.25">
@@ -8136,147 +8112,149 @@
         <v>172</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="E190" s="6"/>
       <c r="F190" s="6" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H190" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I190" s="11">
         <v>44197</v>
       </c>
       <c r="J190" s="10" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="191" spans="2:10" ht="150" x14ac:dyDescent="0.25">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="191" spans="2:10" ht="138" x14ac:dyDescent="0.25">
       <c r="B191" s="6">
         <v>173</v>
       </c>
       <c r="C191" s="7" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="D191" s="7" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="E191" s="7"/>
-      <c r="F191" s="7" t="s">
-        <v>202</v>
+      <c r="F191" s="6" t="s">
+        <v>197</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H191" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I191" s="11">
         <v>45549</v>
       </c>
       <c r="J191" s="10"/>
     </row>
-    <row r="192" spans="2:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:10" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B192" s="6">
         <v>174</v>
       </c>
       <c r="C192" s="7" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="D192" s="7" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F192" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H192" s="7" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="I192" s="14">
         <v>42298</v>
       </c>
       <c r="J192" s="10"/>
     </row>
-    <row r="193" spans="2:10" ht="105" x14ac:dyDescent="0.25">
-      <c r="B193" s="6">
+    <row r="193" spans="2:10" ht="96.6" x14ac:dyDescent="0.25">
+      <c r="B193" s="25">
         <v>175</v>
       </c>
       <c r="C193" s="7" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="D193" s="7" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="E193" s="7" t="s">
-        <v>427</v>
-      </c>
-      <c r="F193" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="G193" s="3" t="s">
-        <v>11</v>
+        <v>588</v>
+      </c>
+      <c r="F193" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="G193" s="24" t="s">
+        <v>579</v>
       </c>
       <c r="H193" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I193" s="14">
         <v>45687</v>
       </c>
       <c r="J193" s="10"/>
     </row>
-    <row r="194" spans="2:10" ht="120" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:10" ht="96.6" x14ac:dyDescent="0.25">
       <c r="B194" s="6">
         <v>176</v>
       </c>
       <c r="C194" s="7" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="D194" s="7" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="E194" s="7"/>
-      <c r="F194" s="7" t="s">
-        <v>208</v>
+      <c r="F194" s="6" t="s">
+        <v>197</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H194" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I194" s="14">
         <v>45623</v>
       </c>
       <c r="J194" s="6" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="195" spans="2:10" ht="90" x14ac:dyDescent="0.25">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="195" spans="2:10" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B195" s="6">
         <v>177</v>
       </c>
       <c r="C195" s="7" t="s">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="D195" s="7" t="s">
-        <v>428</v>
-      </c>
-      <c r="E195" s="7"/>
+        <v>417</v>
+      </c>
+      <c r="E195" s="7" t="s">
+        <v>582</v>
+      </c>
       <c r="F195" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H195" s="6"/>
       <c r="I195" s="14">
@@ -8284,228 +8262,230 @@
       </c>
       <c r="J195" s="10"/>
     </row>
-    <row r="196" spans="2:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:10" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B196" s="6">
         <v>178</v>
       </c>
       <c r="C196" s="7" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="D196" s="7" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="E196" s="7"/>
       <c r="F196" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H196" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I196" s="14">
         <v>45699</v>
       </c>
       <c r="J196" s="10"/>
     </row>
-    <row r="197" spans="2:10" ht="105" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:10" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B197" s="6">
         <v>179</v>
       </c>
       <c r="C197" s="7" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="D197" s="7" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="E197" s="7"/>
-      <c r="F197" s="7" t="s">
-        <v>208</v>
+      <c r="F197" s="6" t="s">
+        <v>197</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H197" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I197" s="14">
         <v>45645</v>
       </c>
       <c r="J197" s="10"/>
     </row>
-    <row r="198" spans="2:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:10" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B198" s="6">
         <v>180</v>
       </c>
       <c r="C198" s="7" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="D198" s="7" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="E198" s="7"/>
-      <c r="F198" s="7" t="s">
-        <v>208</v>
+      <c r="F198" s="6" t="s">
+        <v>197</v>
       </c>
       <c r="G198" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H198" s="7" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="I198" s="15"/>
       <c r="J198" s="10"/>
     </row>
-    <row r="199" spans="2:10" ht="105" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:10" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B199" s="6">
         <v>181</v>
       </c>
       <c r="C199" s="7" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="D199" s="7" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="E199" s="7"/>
-      <c r="F199" s="7" t="s">
-        <v>208</v>
+      <c r="F199" s="6" t="s">
+        <v>197</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H199" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I199" s="14">
         <v>45671</v>
       </c>
       <c r="J199" s="6" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="200" spans="2:10" ht="120" x14ac:dyDescent="0.25">
-      <c r="B200" s="6">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="200" spans="2:10" ht="96.6" x14ac:dyDescent="0.25">
+      <c r="B200" s="25">
         <v>182</v>
       </c>
       <c r="C200" s="7" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="D200" s="7" t="s">
-        <v>440</v>
-      </c>
-      <c r="E200" s="7"/>
+        <v>429</v>
+      </c>
+      <c r="E200" s="7" t="s">
+        <v>590</v>
+      </c>
       <c r="F200" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="G200" s="3" t="s">
-        <v>11</v>
+        <v>65</v>
+      </c>
+      <c r="G200" s="22" t="s">
+        <v>43</v>
       </c>
       <c r="H200" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I200" s="14">
         <v>45743</v>
       </c>
       <c r="J200" s="6" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="201" spans="2:10" ht="105" x14ac:dyDescent="0.25">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="201" spans="2:10" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B201" s="6">
         <v>183</v>
       </c>
       <c r="C201" s="7" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="D201" s="6" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="E201" s="7"/>
-      <c r="F201" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="G201" s="19" t="s">
-        <v>11</v>
+      <c r="F201" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="G201" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H201" s="7" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="I201" s="14">
         <v>45838</v>
       </c>
       <c r="J201" s="10"/>
     </row>
-    <row r="202" spans="2:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:10" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B202" s="6">
         <v>184</v>
       </c>
       <c r="C202" s="7" t="s">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="D202" s="7" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="E202" s="7"/>
-      <c r="F202" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="G202" s="19" t="s">
-        <v>11</v>
+      <c r="F202" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="G202" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H202" s="7" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="I202" s="14">
         <v>45840</v>
       </c>
       <c r="J202" s="10"/>
     </row>
-    <row r="203" spans="2:10" ht="105" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:10" ht="96.6" x14ac:dyDescent="0.25">
       <c r="B203" s="6">
         <v>185</v>
       </c>
       <c r="C203" s="7" t="s">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="D203" s="7" t="s">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="E203" s="7" t="s">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="F203" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="G203" s="19" t="s">
-        <v>11</v>
+        <v>110</v>
+      </c>
+      <c r="G203" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H203" s="7" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="I203" s="14">
         <v>45826</v>
       </c>
       <c r="J203" s="10"/>
     </row>
-    <row r="204" spans="2:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:10" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B204" s="6">
         <v>186</v>
       </c>
       <c r="C204" s="7" t="s">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="D204" s="7" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="E204" s="7" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="F204" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="G204" s="19" t="s">
-        <v>11</v>
+        <v>110</v>
+      </c>
+      <c r="G204" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H204" s="7"/>
       <c r="I204" s="14">
@@ -8513,24 +8493,24 @@
       </c>
       <c r="J204" s="10"/>
     </row>
-    <row r="205" spans="2:10" ht="210" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:10" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B205" s="6">
         <v>187</v>
       </c>
       <c r="C205" s="7" t="s">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="D205" s="7" t="s">
-        <v>473</v>
+        <v>462</v>
       </c>
       <c r="E205" s="7" t="s">
-        <v>474</v>
-      </c>
-      <c r="F205" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="G205" s="19" t="s">
-        <v>11</v>
+        <v>463</v>
+      </c>
+      <c r="F205" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="G205" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H205" s="7"/>
       <c r="I205" s="14">
@@ -8538,24 +8518,24 @@
       </c>
       <c r="J205" s="10"/>
     </row>
-    <row r="206" spans="2:10" ht="135" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:10" ht="124.2" x14ac:dyDescent="0.25">
       <c r="B206" s="6">
         <v>188</v>
       </c>
       <c r="C206" s="7" t="s">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="D206" s="7" t="s">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="E206" s="7" t="s">
-        <v>531</v>
+        <v>520</v>
       </c>
       <c r="F206" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="G206" s="19" t="s">
-        <v>11</v>
+        <v>110</v>
+      </c>
+      <c r="G206" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H206" s="7"/>
       <c r="I206" s="14">
@@ -8563,51 +8543,51 @@
       </c>
       <c r="J206" s="10"/>
     </row>
-    <row r="207" spans="2:10" ht="255" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:10" ht="234.6" x14ac:dyDescent="0.25">
       <c r="B207" s="6">
         <v>189</v>
       </c>
       <c r="C207" s="6" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="D207" s="6" t="s">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="E207" s="6" t="s">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="F207" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="G207" s="19" t="s">
-        <v>11</v>
+        <v>197</v>
+      </c>
+      <c r="G207" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H207" s="6"/>
       <c r="I207" s="11">
         <v>45994</v>
       </c>
       <c r="J207" s="6" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="208" spans="2:10" ht="90" x14ac:dyDescent="0.25">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="208" spans="2:10" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B208" s="6">
         <v>190</v>
       </c>
       <c r="C208" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="D208" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="E208" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="F208" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="G208" s="19" t="s">
-        <v>11</v>
+        <v>197</v>
+      </c>
+      <c r="G208" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H208" s="7"/>
       <c r="I208" s="11">
@@ -8615,24 +8595,24 @@
       </c>
       <c r="J208" s="10"/>
     </row>
-    <row r="209" spans="2:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:10" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B209" s="6">
         <v>191</v>
       </c>
       <c r="C209" s="7" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="D209" s="7" t="s">
-        <v>486</v>
+        <v>475</v>
       </c>
       <c r="E209" s="7" t="s">
-        <v>487</v>
+        <v>476</v>
       </c>
       <c r="F209" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="G209" s="19" t="s">
-        <v>11</v>
+        <v>197</v>
+      </c>
+      <c r="G209" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H209" s="7"/>
       <c r="I209" s="11">
@@ -8640,24 +8620,24 @@
       </c>
       <c r="J209" s="10"/>
     </row>
-    <row r="210" spans="2:10" ht="150" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:10" ht="124.2" x14ac:dyDescent="0.25">
       <c r="B210" s="6">
         <v>192</v>
       </c>
       <c r="C210" s="7" t="s">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="D210" s="7" t="s">
-        <v>489</v>
+        <v>478</v>
       </c>
       <c r="E210" s="7" t="s">
-        <v>490</v>
+        <v>479</v>
       </c>
       <c r="F210" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="G210" s="19" t="s">
-        <v>11</v>
+        <v>197</v>
+      </c>
+      <c r="G210" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H210" s="7"/>
       <c r="I210" s="11">
@@ -8665,24 +8645,24 @@
       </c>
       <c r="J210" s="10"/>
     </row>
-    <row r="211" spans="2:10" ht="150" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:10" ht="138" x14ac:dyDescent="0.25">
       <c r="B211" s="6">
         <v>193</v>
       </c>
       <c r="C211" s="7" t="s">
-        <v>493</v>
+        <v>482</v>
       </c>
       <c r="D211" s="7" t="s">
-        <v>492</v>
+        <v>481</v>
       </c>
       <c r="E211" s="7" t="s">
-        <v>491</v>
+        <v>480</v>
       </c>
       <c r="F211" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="G211" s="19" t="s">
-        <v>11</v>
+        <v>110</v>
+      </c>
+      <c r="G211" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H211" s="7"/>
       <c r="I211" s="14">
@@ -8690,24 +8670,24 @@
       </c>
       <c r="J211" s="10"/>
     </row>
-    <row r="212" spans="2:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:10" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B212" s="6">
         <v>194</v>
       </c>
       <c r="C212" s="7" t="s">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="D212" s="7" t="s">
-        <v>494</v>
+        <v>483</v>
       </c>
       <c r="E212" s="7" t="s">
-        <v>496</v>
+        <v>485</v>
       </c>
       <c r="F212" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="G212" s="19" t="s">
-        <v>11</v>
+        <v>110</v>
+      </c>
+      <c r="G212" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H212" s="7"/>
       <c r="I212" s="14">
@@ -8715,267 +8695,267 @@
       </c>
       <c r="J212" s="10"/>
     </row>
-    <row r="213" spans="2:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="213" spans="2:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B213" s="6">
         <v>195</v>
       </c>
       <c r="C213" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="D213" s="7" t="s">
+        <v>507</v>
+      </c>
+      <c r="E213" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="F213" s="7" t="s">
         <v>498</v>
       </c>
-      <c r="D213" s="7" t="s">
-        <v>518</v>
-      </c>
-      <c r="E213" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="F213" s="7" t="s">
-        <v>509</v>
-      </c>
       <c r="G213" s="19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H213" s="7"/>
       <c r="I213" s="14">
         <v>43006</v>
       </c>
       <c r="J213" s="15" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="214" spans="2:10" ht="45" x14ac:dyDescent="0.25">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="214" spans="2:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B214" s="6">
         <v>196</v>
       </c>
       <c r="C214" s="7" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="D214" s="7" t="s">
-        <v>517</v>
+        <v>506</v>
       </c>
       <c r="E214" s="7" t="s">
-        <v>500</v>
+        <v>489</v>
       </c>
       <c r="F214" s="7" t="s">
-        <v>509</v>
+        <v>498</v>
       </c>
       <c r="G214" s="19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H214" s="7"/>
       <c r="I214" s="14">
         <v>43262</v>
       </c>
       <c r="J214" s="15" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="215" spans="2:10" ht="45" x14ac:dyDescent="0.25">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="215" spans="2:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B215" s="6">
         <v>197</v>
       </c>
       <c r="C215" s="7" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="D215" s="7" t="s">
-        <v>516</v>
+        <v>505</v>
       </c>
       <c r="E215" s="7" t="s">
-        <v>497</v>
+        <v>486</v>
       </c>
       <c r="F215" s="7" t="s">
-        <v>509</v>
+        <v>498</v>
       </c>
       <c r="G215" s="19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H215" s="7"/>
       <c r="I215" s="14">
         <v>44335</v>
       </c>
       <c r="J215" s="15" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="216" spans="2:10" ht="45" x14ac:dyDescent="0.25">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="216" spans="2:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B216" s="6">
         <v>198</v>
       </c>
       <c r="C216" s="7" t="s">
+        <v>493</v>
+      </c>
+      <c r="D216" s="7" t="s">
         <v>504</v>
       </c>
-      <c r="D216" s="7" t="s">
-        <v>515</v>
-      </c>
       <c r="E216" s="7" t="s">
-        <v>503</v>
+        <v>492</v>
       </c>
       <c r="F216" s="7" t="s">
-        <v>509</v>
+        <v>498</v>
       </c>
       <c r="G216" s="19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H216" s="7"/>
       <c r="I216" s="14">
         <v>44212</v>
       </c>
       <c r="J216" s="15" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="217" spans="2:10" ht="45" x14ac:dyDescent="0.25">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="217" spans="2:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B217" s="6">
         <v>199</v>
       </c>
       <c r="C217" s="7" t="s">
-        <v>505</v>
+        <v>494</v>
       </c>
       <c r="D217" s="7" t="s">
-        <v>514</v>
+        <v>503</v>
       </c>
       <c r="E217" s="7" t="s">
-        <v>506</v>
+        <v>495</v>
       </c>
       <c r="F217" s="7" t="s">
-        <v>509</v>
+        <v>498</v>
       </c>
       <c r="G217" s="19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H217" s="7"/>
       <c r="I217" s="14">
         <v>44785</v>
       </c>
       <c r="J217" s="15" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="218" spans="2:10" ht="45" x14ac:dyDescent="0.25">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="218" spans="2:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B218" s="6">
         <v>200</v>
       </c>
       <c r="C218" s="7" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
       <c r="D218" s="7" t="s">
-        <v>513</v>
+        <v>502</v>
       </c>
       <c r="E218" s="7" t="s">
-        <v>507</v>
+        <v>496</v>
       </c>
       <c r="F218" s="7" t="s">
-        <v>509</v>
+        <v>498</v>
       </c>
       <c r="G218" s="19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H218" s="7"/>
       <c r="I218" s="14">
         <v>43648</v>
       </c>
       <c r="J218" s="15" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="219" spans="2:10" ht="45" x14ac:dyDescent="0.25">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="219" spans="2:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B219" s="6">
         <v>201</v>
       </c>
       <c r="C219" s="7" t="s">
-        <v>511</v>
+        <v>500</v>
       </c>
       <c r="D219" s="7" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
       <c r="E219" s="7" t="s">
-        <v>510</v>
+        <v>499</v>
       </c>
       <c r="F219" s="7" t="s">
-        <v>509</v>
+        <v>498</v>
       </c>
       <c r="G219" s="19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H219" s="7"/>
       <c r="I219" s="14">
         <v>45894</v>
       </c>
       <c r="J219" s="15" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="220" spans="2:10" ht="75" x14ac:dyDescent="0.25">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="220" spans="2:10" ht="69" x14ac:dyDescent="0.25">
       <c r="B220" s="6">
         <v>202</v>
       </c>
       <c r="C220" s="7" t="s">
-        <v>524</v>
+        <v>513</v>
       </c>
       <c r="D220" s="7" t="s">
-        <v>523</v>
+        <v>512</v>
       </c>
       <c r="E220" s="7" t="s">
-        <v>527</v>
+        <v>516</v>
       </c>
       <c r="F220" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="G220" s="19" t="s">
-        <v>11</v>
+        <v>110</v>
+      </c>
+      <c r="G220" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H220" s="7"/>
       <c r="I220" s="14">
         <v>45471</v>
       </c>
       <c r="J220" s="15" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="221" spans="2:10" ht="150" x14ac:dyDescent="0.25">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="221" spans="2:10" ht="138" x14ac:dyDescent="0.25">
       <c r="B221" s="6">
         <v>203</v>
       </c>
       <c r="C221" s="7" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D221" s="7" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="E221" s="7" t="s">
-        <v>530</v>
+        <v>519</v>
       </c>
       <c r="F221" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="G221" s="19" t="s">
-        <v>11</v>
+        <v>110</v>
+      </c>
+      <c r="G221" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H221" s="7"/>
       <c r="I221" s="14">
         <v>46022</v>
       </c>
       <c r="J221" s="15" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="222" spans="2:10" ht="105" x14ac:dyDescent="0.25">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="222" spans="2:10" ht="96.6" x14ac:dyDescent="0.25">
       <c r="B222" s="6">
         <v>204</v>
       </c>
       <c r="C222" s="7" t="s">
-        <v>532</v>
+        <v>521</v>
       </c>
       <c r="D222" s="7" t="s">
-        <v>533</v>
+        <v>522</v>
       </c>
       <c r="E222" s="7" t="s">
-        <v>534</v>
+        <v>523</v>
       </c>
       <c r="F222" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="G222" s="19" t="s">
-        <v>11</v>
+        <v>110</v>
+      </c>
+      <c r="G222" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H222" s="7"/>
       <c r="I222" s="14">
@@ -8983,24 +8963,24 @@
       </c>
       <c r="J222" s="15"/>
     </row>
-    <row r="223" spans="2:10" ht="240" x14ac:dyDescent="0.25">
+    <row r="223" spans="2:10" ht="207" x14ac:dyDescent="0.25">
       <c r="B223" s="6">
         <v>205</v>
       </c>
       <c r="C223" s="7" t="s">
-        <v>536</v>
+        <v>525</v>
       </c>
       <c r="D223" s="7" t="s">
-        <v>535</v>
+        <v>524</v>
       </c>
       <c r="E223" s="7" t="s">
-        <v>537</v>
+        <v>526</v>
       </c>
       <c r="F223" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="G223" s="19" t="s">
-        <v>11</v>
+        <v>110</v>
+      </c>
+      <c r="G223" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H223" s="7"/>
       <c r="I223" s="14">
@@ -9008,24 +8988,24 @@
       </c>
       <c r="J223" s="15"/>
     </row>
-    <row r="224" spans="2:10" ht="270" x14ac:dyDescent="0.25">
+    <row r="224" spans="2:10" ht="234.6" x14ac:dyDescent="0.25">
       <c r="B224" s="6">
         <v>206</v>
       </c>
       <c r="C224" s="7" t="s">
-        <v>538</v>
+        <v>527</v>
       </c>
       <c r="D224" s="7" t="s">
-        <v>539</v>
+        <v>528</v>
       </c>
       <c r="E224" s="7" t="s">
-        <v>540</v>
+        <v>529</v>
       </c>
       <c r="F224" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="G224" s="19" t="s">
-        <v>11</v>
+        <v>110</v>
+      </c>
+      <c r="G224" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H224" s="7"/>
       <c r="I224" s="14">
@@ -9033,24 +9013,24 @@
       </c>
       <c r="J224" s="15"/>
     </row>
-    <row r="225" spans="2:10" ht="165" x14ac:dyDescent="0.25">
+    <row r="225" spans="2:10" ht="151.80000000000001" x14ac:dyDescent="0.25">
       <c r="B225" s="6">
         <v>207</v>
       </c>
       <c r="C225" s="7" t="s">
-        <v>541</v>
+        <v>530</v>
       </c>
       <c r="D225" s="7" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="E225" s="7" t="s">
-        <v>543</v>
+        <v>532</v>
       </c>
       <c r="F225" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="G225" s="19" t="s">
-        <v>11</v>
+        <v>110</v>
+      </c>
+      <c r="G225" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H225" s="7"/>
       <c r="I225" s="14">
@@ -9058,22 +9038,22 @@
       </c>
       <c r="J225" s="15"/>
     </row>
-    <row r="226" spans="2:10" ht="105" x14ac:dyDescent="0.25">
+    <row r="226" spans="2:10" ht="96.6" x14ac:dyDescent="0.25">
       <c r="B226" s="6">
         <v>208</v>
       </c>
       <c r="C226" s="7" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
       <c r="D226" s="7" t="s">
-        <v>547</v>
+        <v>536</v>
       </c>
       <c r="E226" s="7"/>
-      <c r="F226" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="G226" s="19" t="s">
-        <v>11</v>
+      <c r="F226" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="G226" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H226" s="7"/>
       <c r="I226" s="14">
@@ -9081,22 +9061,22 @@
       </c>
       <c r="J226" s="15"/>
     </row>
-    <row r="227" spans="2:10" ht="120" x14ac:dyDescent="0.25">
+    <row r="227" spans="2:10" ht="96.6" x14ac:dyDescent="0.25">
       <c r="B227" s="6">
         <v>209</v>
       </c>
       <c r="C227" s="7" t="s">
-        <v>545</v>
+        <v>534</v>
       </c>
       <c r="D227" s="7" t="s">
-        <v>546</v>
+        <v>535</v>
       </c>
       <c r="E227" s="7"/>
-      <c r="F227" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="G227" s="19" t="s">
-        <v>11</v>
+      <c r="F227" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="G227" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H227" s="7"/>
       <c r="I227" s="14">
@@ -9104,22 +9084,22 @@
       </c>
       <c r="J227" s="15"/>
     </row>
-    <row r="228" spans="2:10" ht="195" x14ac:dyDescent="0.25">
+    <row r="228" spans="2:10" ht="179.4" x14ac:dyDescent="0.25">
       <c r="B228" s="6">
         <v>210</v>
       </c>
       <c r="C228" s="7" t="s">
-        <v>548</v>
+        <v>537</v>
       </c>
       <c r="D228" s="7" t="s">
-        <v>551</v>
+        <v>540</v>
       </c>
       <c r="E228" s="7"/>
-      <c r="F228" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="G228" s="19" t="s">
-        <v>11</v>
+      <c r="F228" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="G228" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H228" s="7"/>
       <c r="I228" s="14">
@@ -9127,278 +9107,330 @@
       </c>
       <c r="J228" s="15"/>
     </row>
-    <row r="229" spans="2:10" ht="135" x14ac:dyDescent="0.25">
-      <c r="B229" s="21">
+    <row r="229" spans="2:10" ht="124.2" x14ac:dyDescent="0.25">
+      <c r="B229" s="7">
         <v>211</v>
       </c>
-      <c r="C229" s="21" t="s">
-        <v>552</v>
-      </c>
-      <c r="D229" s="21" t="s">
-        <v>553</v>
-      </c>
-      <c r="E229" s="21"/>
-      <c r="F229" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="G229" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="H229" s="21"/>
+      <c r="C229" s="7" t="s">
+        <v>541</v>
+      </c>
+      <c r="D229" s="7" t="s">
+        <v>542</v>
+      </c>
+      <c r="E229" s="7"/>
+      <c r="F229" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="G229" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H229" s="7"/>
       <c r="I229" s="14">
         <v>46043</v>
       </c>
-      <c r="J229" s="22"/>
-    </row>
-    <row r="230" spans="2:10" ht="135" x14ac:dyDescent="0.25">
+      <c r="J229" s="15"/>
+    </row>
+    <row r="230" spans="2:10" ht="110.4" x14ac:dyDescent="0.25">
       <c r="B230" s="6">
         <v>212</v>
       </c>
-      <c r="C230" s="21" t="s">
-        <v>554</v>
-      </c>
-      <c r="D230" s="21" t="s">
-        <v>556</v>
-      </c>
-      <c r="E230" s="21" t="s">
-        <v>555</v>
-      </c>
-      <c r="F230" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="G230" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="H230" s="21"/>
+      <c r="C230" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="D230" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="E230" s="7" t="s">
+        <v>589</v>
+      </c>
+      <c r="F230" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="G230" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H230" s="7"/>
       <c r="I230" s="14">
         <v>46052</v>
       </c>
-      <c r="J230" s="22"/>
-    </row>
-    <row r="231" spans="2:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="J230" s="15"/>
+    </row>
+    <row r="231" spans="2:10" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B231" s="6">
         <v>213</v>
       </c>
-      <c r="C231" s="21" t="s">
-        <v>557</v>
-      </c>
-      <c r="D231" s="21" t="s">
-        <v>559</v>
-      </c>
-      <c r="E231" s="21"/>
-      <c r="F231" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="G231" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="H231" s="21"/>
+      <c r="C231" s="7" t="s">
+        <v>545</v>
+      </c>
+      <c r="D231" s="7" t="s">
+        <v>547</v>
+      </c>
+      <c r="E231" s="7"/>
+      <c r="F231" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="G231" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H231" s="7"/>
       <c r="I231" s="14">
         <v>46071</v>
       </c>
-      <c r="J231" s="22"/>
-    </row>
-    <row r="232" spans="2:10" ht="150" x14ac:dyDescent="0.25">
-      <c r="B232" s="21">
+      <c r="J231" s="15"/>
+    </row>
+    <row r="232" spans="2:10" ht="124.2" x14ac:dyDescent="0.25">
+      <c r="B232" s="7">
         <v>214</v>
       </c>
-      <c r="C232" s="21" t="s">
+      <c r="C232" s="7" t="s">
+        <v>546</v>
+      </c>
+      <c r="D232" s="7" t="s">
+        <v>548</v>
+      </c>
+      <c r="E232" s="7" t="s">
         <v>558</v>
       </c>
-      <c r="D232" s="21" t="s">
-        <v>560</v>
-      </c>
-      <c r="E232" s="21" t="s">
-        <v>570</v>
-      </c>
-      <c r="F232" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="G232" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="H232" s="21"/>
+      <c r="F232" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="G232" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H232" s="7"/>
       <c r="I232" s="14">
         <v>46071</v>
       </c>
-      <c r="J232" s="22"/>
-    </row>
-    <row r="233" spans="2:10" ht="165" x14ac:dyDescent="0.25">
+      <c r="J232" s="15"/>
+    </row>
+    <row r="233" spans="2:10" ht="151.80000000000001" x14ac:dyDescent="0.25">
       <c r="B233" s="6">
         <v>215</v>
       </c>
-      <c r="C233" s="21" t="s">
-        <v>562</v>
-      </c>
-      <c r="D233" s="21" t="s">
-        <v>561</v>
-      </c>
-      <c r="E233" s="21" t="s">
-        <v>563</v>
-      </c>
-      <c r="F233" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="G233" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="H233" s="21"/>
+      <c r="C233" s="7" t="s">
+        <v>550</v>
+      </c>
+      <c r="D233" s="7" t="s">
+        <v>549</v>
+      </c>
+      <c r="E233" s="7" t="s">
+        <v>551</v>
+      </c>
+      <c r="F233" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="G233" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H233" s="7"/>
       <c r="I233" s="14">
         <v>46076</v>
       </c>
-      <c r="J233" s="22"/>
-    </row>
-    <row r="234" spans="2:10" ht="225" x14ac:dyDescent="0.25">
+      <c r="J233" s="15"/>
+    </row>
+    <row r="234" spans="2:10" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B234" s="6">
         <v>216</v>
       </c>
-      <c r="C234" s="21" t="s">
+      <c r="C234" s="7" t="s">
+        <v>554</v>
+      </c>
+      <c r="D234" s="7" t="s">
+        <v>552</v>
+      </c>
+      <c r="E234" s="7" t="s">
+        <v>553</v>
+      </c>
+      <c r="F234" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="G234" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H234" s="7"/>
+      <c r="I234" s="14">
+        <v>45681</v>
+      </c>
+      <c r="J234" s="15" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="235" spans="2:10" ht="69" x14ac:dyDescent="0.25">
+      <c r="B235" s="7">
+        <v>217</v>
+      </c>
+      <c r="C235" s="7" t="s">
+        <v>555</v>
+      </c>
+      <c r="D235" s="7" t="s">
+        <v>556</v>
+      </c>
+      <c r="E235" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="F235" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="G235" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H235" s="7"/>
+      <c r="I235" s="14">
+        <v>46050</v>
+      </c>
+      <c r="J235" s="15" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="236" spans="2:10" ht="276" x14ac:dyDescent="0.25">
+      <c r="B236" s="7">
+        <v>218</v>
+      </c>
+      <c r="C236" s="7" t="s">
+        <v>561</v>
+      </c>
+      <c r="D236" s="7" t="s">
+        <v>560</v>
+      </c>
+      <c r="E236" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="F236" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="G236" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H236" s="7"/>
+      <c r="I236" s="14">
+        <v>46008</v>
+      </c>
+      <c r="J236" s="15"/>
+    </row>
+    <row r="237" spans="2:10" ht="138" x14ac:dyDescent="0.25">
+      <c r="B237" s="7">
+        <v>219</v>
+      </c>
+      <c r="C237" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="D237" s="7" t="s">
+        <v>564</v>
+      </c>
+      <c r="E237" s="7" t="s">
+        <v>591</v>
+      </c>
+      <c r="F237" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="G237" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H237" s="7"/>
+      <c r="I237" s="14">
+        <v>45874</v>
+      </c>
+      <c r="J237" s="15"/>
+    </row>
+    <row r="238" spans="2:10" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="B238" s="7">
+        <v>220</v>
+      </c>
+      <c r="C238" s="7" t="s">
+        <v>567</v>
+      </c>
+      <c r="D238" s="7" t="s">
         <v>566</v>
       </c>
-      <c r="D234" s="21" t="s">
-        <v>564</v>
-      </c>
-      <c r="E234" s="21" t="s">
+      <c r="E238" s="7" t="s">
         <v>565</v>
       </c>
-      <c r="F234" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="G234" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="H234" s="21"/>
-      <c r="I234" s="23">
-        <v>45681</v>
-      </c>
-      <c r="J234" s="22" t="s">
+      <c r="F238" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="G238" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H238" s="7"/>
+      <c r="I238" s="14">
+        <v>46010</v>
+      </c>
+      <c r="J238" s="15"/>
+    </row>
+    <row r="239" spans="2:10" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="B239" s="7">
+        <v>221</v>
+      </c>
+      <c r="C239" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="D239" s="7" t="s">
+        <v>568</v>
+      </c>
+      <c r="E239" s="7" t="s">
+        <v>570</v>
+      </c>
+      <c r="F239" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="G239" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H239" s="7"/>
+      <c r="I239" s="14">
+        <v>45826</v>
+      </c>
+      <c r="J239" s="15"/>
+    </row>
+    <row r="240" spans="2:10" ht="96.6" x14ac:dyDescent="0.25">
+      <c r="B240" s="7">
+        <v>222</v>
+      </c>
+      <c r="C240" s="7" t="s">
         <v>571</v>
       </c>
-    </row>
-    <row r="235" spans="2:10" ht="90" x14ac:dyDescent="0.25">
-      <c r="B235" s="21">
-        <v>217</v>
-      </c>
-      <c r="C235" s="21" t="s">
-        <v>567</v>
-      </c>
-      <c r="D235" s="21" t="s">
-        <v>568</v>
-      </c>
-      <c r="E235" s="21" t="s">
-        <v>569</v>
-      </c>
-      <c r="F235" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="G235" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="H235" s="21"/>
-      <c r="I235" s="23">
-        <v>46050</v>
-      </c>
-      <c r="J235" s="22" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="236" spans="2:10" ht="300" x14ac:dyDescent="0.25">
-      <c r="B236" s="21">
-        <v>218</v>
-      </c>
-      <c r="C236" s="21" t="s">
+      <c r="D240" s="7" t="s">
+        <v>572</v>
+      </c>
+      <c r="E240" s="7" t="s">
         <v>573</v>
       </c>
-      <c r="D236" s="21" t="s">
-        <v>572</v>
-      </c>
-      <c r="E236" s="21" t="s">
+      <c r="F240" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="G240" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H240" s="7"/>
+      <c r="I240" s="14">
+        <v>46128</v>
+      </c>
+      <c r="J240" s="15"/>
+    </row>
+    <row r="241" spans="2:10" ht="69" x14ac:dyDescent="0.25">
+      <c r="B241" s="6">
+        <v>223</v>
+      </c>
+      <c r="C241" s="6" t="s">
         <v>574</v>
       </c>
-      <c r="F236" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="G236" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="H236" s="21"/>
-      <c r="I236" s="23">
-        <v>46008</v>
-      </c>
-      <c r="J236" s="22"/>
-    </row>
-    <row r="237" spans="2:10" ht="165" x14ac:dyDescent="0.25">
-      <c r="B237" s="21">
-        <v>219</v>
-      </c>
-      <c r="C237" s="21" t="s">
+      <c r="D241" s="6" t="s">
         <v>575</v>
       </c>
-      <c r="D237" s="21" t="s">
+      <c r="E241" s="6" t="s">
         <v>576</v>
       </c>
-      <c r="E237" s="21"/>
-      <c r="F237" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="G237" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="H237" s="21"/>
-      <c r="I237" s="23">
-        <v>45874</v>
-      </c>
-      <c r="J237" s="22"/>
-    </row>
-    <row r="238" spans="2:10" ht="180" x14ac:dyDescent="0.25">
-      <c r="B238" s="21">
-        <v>220</v>
-      </c>
-      <c r="C238" s="21" t="s">
-        <v>579</v>
-      </c>
-      <c r="D238" s="21" t="s">
-        <v>578</v>
-      </c>
-      <c r="E238" s="21" t="s">
-        <v>577</v>
-      </c>
-      <c r="F238" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="G238" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="H238" s="21"/>
-      <c r="I238" s="23">
-        <v>46010</v>
-      </c>
-      <c r="J238" s="22"/>
-    </row>
-    <row r="239" spans="2:10" ht="165" x14ac:dyDescent="0.25">
-      <c r="B239" s="21">
-        <v>221</v>
-      </c>
-      <c r="C239" s="21" t="s">
-        <v>581</v>
-      </c>
-      <c r="D239" s="21" t="s">
-        <v>580</v>
-      </c>
-      <c r="E239" s="21" t="s">
-        <v>582</v>
-      </c>
-      <c r="F239" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="G239" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="H239" s="21"/>
-      <c r="I239" s="23">
-        <v>45826</v>
-      </c>
-      <c r="J239" s="22"/>
+      <c r="F241" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="G241" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H241" s="6"/>
+      <c r="I241" s="11">
+        <v>46086</v>
+      </c>
+      <c r="J241" s="10"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G193:H197">
@@ -9407,37 +9439,94 @@
   <mergeCells count="1">
     <mergeCell ref="C2:H2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G19:G239">
-    <cfRule type="cellIs" dxfId="35" priority="1" operator="equal">
+  <conditionalFormatting sqref="G19:G35 G62 G69 G75 G77 G85 G89 G93:G95 G154:G190 G193 G200 G213:G219">
+    <cfRule type="cellIs" dxfId="23" priority="17" operator="equal">
       <formula>"Невідомо"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="18" operator="equal">
       <formula>"Застосовно (з приміткою)"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="19" operator="equal">
       <formula>"Застосовно"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="20" operator="equal">
       <formula>"Не застосовно"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H10:H12 H14:H15">
-    <cfRule type="cellIs" dxfId="31" priority="5" operator="equal">
+  <conditionalFormatting sqref="H11 H14:H15">
+    <cfRule type="cellIs" dxfId="31" priority="21" operator="equal">
       <formula>"Невідомо"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="22" operator="equal">
       <formula>"Застосовно (з приміткою)"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="23" operator="equal">
       <formula>"Застосовно"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="24" operator="equal">
+      <formula>"Не застосовно"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
+    <cfRule type="cellIs" dxfId="15" priority="13" operator="equal">
+      <formula>"Невідомо"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="14" operator="equal">
+      <formula>"Застосовно (з приміткою)"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="15" operator="equal">
+      <formula>"Застосовно"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="16" operator="equal">
+      <formula>"Не застосовно"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H9:H10">
+    <cfRule type="cellIs" dxfId="11" priority="9" operator="equal">
+      <formula>"Невідомо"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="10" operator="equal">
+      <formula>"Застосовно (з приміткою)"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
+      <formula>"Застосовно"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="12" operator="equal">
+      <formula>"Не застосовно"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G220:G241 G201:G212 G194:G199 G191:G192 G96:G153 G90:G92 G86:G88 G78:G84 G76 G70:G74 G63:G68 G36:G61">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
+      <formula>"Невідомо"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
+      <formula>"Застосовно (з приміткою)"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
+      <formula>"Застосовно"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
+      <formula>"Не застосовно"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+      <formula>"Невідомо"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+      <formula>"Застосовно (з приміткою)"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+      <formula>"Застосовно"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"Не застосовно"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -9445,220 +9534,220 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C79120FD-74A7-4689-B3C4-1182B48EEDA5}">
   <dimension ref="B2:I10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="5.28515625" customWidth="1"/>
-    <col min="3" max="3" width="31.5703125" customWidth="1"/>
-    <col min="4" max="4" width="48.140625" customWidth="1"/>
-    <col min="5" max="5" width="62.140625" customWidth="1"/>
-    <col min="6" max="6" width="34.5703125" customWidth="1"/>
-    <col min="7" max="7" width="19.7109375" customWidth="1"/>
-    <col min="8" max="8" width="18.5703125" customWidth="1"/>
-    <col min="9" max="9" width="19.28515625" customWidth="1"/>
+    <col min="2" max="2" width="5.33203125" customWidth="1"/>
+    <col min="3" max="3" width="31.5546875" customWidth="1"/>
+    <col min="4" max="4" width="48.109375" customWidth="1"/>
+    <col min="5" max="5" width="62.109375" customWidth="1"/>
+    <col min="6" max="6" width="34.5546875" customWidth="1"/>
+    <col min="7" max="7" width="19.6640625" customWidth="1"/>
+    <col min="8" max="8" width="18.5546875" customWidth="1"/>
+    <col min="9" max="9" width="19.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>20</v>
-      </c>
       <c r="I2" s="5" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" ht="60" x14ac:dyDescent="0.25">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B3" s="16">
         <v>1</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="E3" s="16"/>
       <c r="F3" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H3" s="16"/>
       <c r="I3" s="17">
         <v>43117</v>
       </c>
     </row>
-    <row r="4" spans="2:9" ht="90" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:9" ht="72" x14ac:dyDescent="0.3">
       <c r="B4" s="16">
         <v>2</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="E4" s="16"/>
       <c r="F4" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H4" s="16"/>
       <c r="I4" s="17">
         <v>45674</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="150" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:9" ht="129.6" x14ac:dyDescent="0.3">
       <c r="B5" s="16">
         <v>3</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="E5" s="16"/>
       <c r="F5" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H5" s="16"/>
       <c r="I5" s="17">
         <v>43446</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="150" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9" ht="129.6" x14ac:dyDescent="0.3">
       <c r="B6" s="16">
         <v>4</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="E6" s="16"/>
       <c r="F6" s="6" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H6" s="16"/>
       <c r="I6" s="17">
         <v>42173</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="90" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="B7" s="16">
         <v>5</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="E7" s="16"/>
       <c r="F7" s="6" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H7" s="16"/>
       <c r="I7" s="17">
         <v>44440</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="90" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:9" ht="82.8" x14ac:dyDescent="0.3">
       <c r="B8" s="16">
         <v>6</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="11">
         <v>43350</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9" ht="69" x14ac:dyDescent="0.3">
       <c r="B9" s="16">
         <v>7</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="11">
         <v>42965</v>
       </c>
     </row>
-    <row r="10" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B10" s="16">
         <v>8</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="11">

--- a/Застосовне законодавство.xlsx
+++ b/Застосовне законодавство.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\користувач\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{37E2801C-5692-49AC-97F1-7FDD9E6B9114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD2A989-A624-4835-8D86-402110D3BAEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{334805C5-B449-4CB8-AF80-1835CA06DE69}"/>
   </bookViews>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="593">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1288" uniqueCount="596">
   <si>
     <t>- В цьому реєстрі перераховані тільки основні законодавчі акти, не враховуючи супутні акти, що затверджують зміни, або покладають завдання з реалізації, наприклад, Національної стратегії кібербезпеки.
 - Сайт ВРУ - основне джерело інформації, оскільки на ньому можна відстежувати актуальність законодавчих актів.</t>
@@ -2043,6 +2043,15 @@
       </rPr>
       <t xml:space="preserve"> Див. Постанова Кабінету Міністрів України від 21 лютого 2025 р. № 205 "Деякі питання створення, адміністрування та забезпечення функціонування засобу інформатизації"</t>
     </r>
+  </si>
+  <si>
+    <t>https://zakon.rada.gov.ua/laws/show/v0067500-24#Text</t>
+  </si>
+  <si>
+    <t>Постанова Національного банку України від 14.06.2024 № 67 "Про затвердження Положення про організацію забезпечення безперебійного функціонування в умовах особливого періоду банківської системи України, діяльності небанківських фінансових установ та інших осіб, які не є фінансовими установами, але мають право надавати окремі фінансові послуги, регулювання та нагляд за діяльністю яких здійснює Національний банк України"</t>
+  </si>
+  <si>
+    <t>Це Положення [..] визначає особливості їх функціонування та діяльності, а також здійснення Національним банком нагляду за їх діяльністю у разі настання особливого періоду.</t>
   </si>
 </sst>
 </file>
@@ -2195,7 +2204,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2252,9 +2261,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2267,194 +2273,23 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="45">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="29">
     <dxf>
       <font>
         <b/>
@@ -3082,21 +2917,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FE4F2F92-58E2-48B9-A7D4-627EBB6ED48E}" name="Таблиця2" displayName="Таблиця2" ref="B18:J241" totalsRowShown="0" headerRowDxfId="44" dataDxfId="42" headerRowBorderDxfId="43" tableBorderDxfId="41">
-  <autoFilter ref="B18:J241" xr:uid="{FE4F2F92-58E2-48B9-A7D4-627EBB6ED48E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FE4F2F92-58E2-48B9-A7D4-627EBB6ED48E}" name="Таблиця2" displayName="Таблиця2" ref="B18:J242" totalsRowShown="0" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25">
+  <autoFilter ref="B18:J242" xr:uid="{FE4F2F92-58E2-48B9-A7D4-627EBB6ED48E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B19:I200">
     <sortCondition ref="B18:B200"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{DFA9E46C-509D-4A00-A369-7966EED6B176}" name="№" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{981014D8-EFBF-47F5-B054-36010B7987AF}" name="Джерело вимог" dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{928FBB84-B24F-469A-AFD2-7EA49120BF89}" name="Посилання" dataDxfId="38"/>
-    <tableColumn id="4" xr3:uid="{D49602E6-E651-4C6D-8A88-C8DCD8A3AFDD}" name="Коментар" dataDxfId="37"/>
-    <tableColumn id="6" xr3:uid="{52AE3B44-6A02-4F51-99B9-C7E17C080BEC}" name="Категорія" dataDxfId="36"/>
-    <tableColumn id="8" xr3:uid="{DE39899F-E232-40DC-A0D1-10B3A973A842}" name="Застосовність" dataDxfId="35"/>
-    <tableColumn id="10" xr3:uid="{40F3EA47-8E92-48F7-A24A-6369E84EA096}" name="Теги" dataDxfId="34"/>
-    <tableColumn id="5" xr3:uid="{A1D4F9E4-94BB-4008-834E-B5DC4DE59C40}" name="Дата прийняття" dataDxfId="33"/>
-    <tableColumn id="7" xr3:uid="{2B27F073-AE91-4210-B0D6-642DEFE05F63}" name="Галузь" dataDxfId="32"/>
+    <tableColumn id="1" xr3:uid="{DFA9E46C-509D-4A00-A369-7966EED6B176}" name="№" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{981014D8-EFBF-47F5-B054-36010B7987AF}" name="Джерело вимог" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{928FBB84-B24F-469A-AFD2-7EA49120BF89}" name="Посилання" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{D49602E6-E651-4C6D-8A88-C8DCD8A3AFDD}" name="Коментар" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{52AE3B44-6A02-4F51-99B9-C7E17C080BEC}" name="Категорія" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{DE39899F-E232-40DC-A0D1-10B3A973A842}" name="Застосовність" dataDxfId="19"/>
+    <tableColumn id="10" xr3:uid="{40F3EA47-8E92-48F7-A24A-6369E84EA096}" name="Теги" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{A1D4F9E4-94BB-4008-834E-B5DC4DE59C40}" name="Дата прийняття" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{2B27F073-AE91-4210-B0D6-642DEFE05F63}" name="Галузь" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3399,7 +3234,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B971BF4-F5CF-496D-9610-E7CBA5A28B9C}">
-  <dimension ref="A2:J241"/>
+  <dimension ref="A2:J242"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
@@ -3416,14 +3251,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="2"/>
@@ -3501,7 +3336,7 @@
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
-      <c r="H9" s="22" t="s">
+      <c r="H9" s="21" t="s">
         <v>43</v>
       </c>
     </row>
@@ -3516,7 +3351,7 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-      <c r="H10" s="22" t="s">
+      <c r="H10" s="21" t="s">
         <v>578</v>
       </c>
     </row>
@@ -3546,7 +3381,7 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="H12" s="21" t="s">
+      <c r="H12" s="20" t="s">
         <v>577</v>
       </c>
     </row>
@@ -3561,7 +3396,7 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
-      <c r="H13" s="24" t="s">
+      <c r="H13" s="23" t="s">
         <v>579</v>
       </c>
     </row>
@@ -4804,7 +4639,7 @@
     </row>
     <row r="62" spans="1:10" ht="193.2" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
-      <c r="B62" s="25">
+      <c r="B62" s="6">
         <v>44</v>
       </c>
       <c r="C62" s="6" t="s">
@@ -4819,7 +4654,7 @@
       <c r="F62" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="G62" s="24" t="s">
+      <c r="G62" s="23" t="s">
         <v>579</v>
       </c>
       <c r="H62" s="6" t="s">
@@ -4998,7 +4833,7 @@
     </row>
     <row r="69" spans="1:10" ht="124.2" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
-      <c r="B69" s="25">
+      <c r="B69" s="6">
         <v>51</v>
       </c>
       <c r="C69" s="6" t="s">
@@ -5013,7 +4848,7 @@
       <c r="F69" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="G69" s="24" t="s">
+      <c r="G69" s="23" t="s">
         <v>579</v>
       </c>
       <c r="H69" s="6"/>
@@ -5164,7 +4999,7 @@
     </row>
     <row r="75" spans="1:10" ht="196.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="4"/>
-      <c r="B75" s="25">
+      <c r="B75" s="6">
         <v>57</v>
       </c>
       <c r="C75" s="6" t="s">
@@ -5179,7 +5014,7 @@
       <c r="F75" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="G75" s="24" t="s">
+      <c r="G75" s="23" t="s">
         <v>579</v>
       </c>
       <c r="H75" s="6" t="s">
@@ -5218,7 +5053,7 @@
     </row>
     <row r="77" spans="1:10" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A77" s="4"/>
-      <c r="B77" s="25">
+      <c r="B77" s="6">
         <v>59</v>
       </c>
       <c r="C77" s="6" t="s">
@@ -5233,7 +5068,7 @@
       <c r="F77" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="G77" s="24" t="s">
+      <c r="G77" s="23" t="s">
         <v>579</v>
       </c>
       <c r="H77" s="6"/>
@@ -5456,7 +5291,7 @@
       <c r="F85" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="G85" s="24" t="s">
+      <c r="G85" s="23" t="s">
         <v>579</v>
       </c>
       <c r="H85" s="6" t="s">
@@ -5522,13 +5357,13 @@
       <c r="J87" s="10"/>
     </row>
     <row r="88" spans="1:10" ht="96.6" x14ac:dyDescent="0.25">
-      <c r="B88" s="25">
+      <c r="B88" s="6">
         <v>70</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="D88" s="23" t="s">
+      <c r="D88" s="22" t="s">
         <v>581</v>
       </c>
       <c r="E88" s="6" t="s">
@@ -5549,7 +5384,7 @@
       <c r="J88" s="10"/>
     </row>
     <row r="89" spans="1:10" ht="289.8" x14ac:dyDescent="0.25">
-      <c r="B89" s="25">
+      <c r="B89" s="6">
         <v>71</v>
       </c>
       <c r="C89" s="6" t="s">
@@ -5564,7 +5399,7 @@
       <c r="F89" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="G89" s="24" t="s">
+      <c r="G89" s="23" t="s">
         <v>579</v>
       </c>
       <c r="H89" s="6"/>
@@ -8184,7 +8019,7 @@
       <c r="J192" s="10"/>
     </row>
     <row r="193" spans="2:10" ht="96.6" x14ac:dyDescent="0.25">
-      <c r="B193" s="25">
+      <c r="B193" s="6">
         <v>175</v>
       </c>
       <c r="C193" s="7" t="s">
@@ -8199,7 +8034,7 @@
       <c r="F193" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="G193" s="24" t="s">
+      <c r="G193" s="23" t="s">
         <v>579</v>
       </c>
       <c r="H193" s="7" t="s">
@@ -8363,7 +8198,7 @@
       </c>
     </row>
     <row r="200" spans="2:10" ht="96.6" x14ac:dyDescent="0.25">
-      <c r="B200" s="25">
+      <c r="B200" s="6">
         <v>182</v>
       </c>
       <c r="C200" s="7" t="s">
@@ -8378,7 +8213,7 @@
       <c r="F200" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="G200" s="22" t="s">
+      <c r="G200" s="21" t="s">
         <v>43</v>
       </c>
       <c r="H200" s="7" t="s">
@@ -9431,6 +9266,33 @@
         <v>46086</v>
       </c>
       <c r="J241" s="10"/>
+    </row>
+    <row r="242" spans="2:10" ht="207" x14ac:dyDescent="0.25">
+      <c r="B242" s="25">
+        <v>224</v>
+      </c>
+      <c r="C242" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="D242" s="25" t="s">
+        <v>593</v>
+      </c>
+      <c r="E242" s="25" t="s">
+        <v>595</v>
+      </c>
+      <c r="F242" s="25" t="s">
+        <v>498</v>
+      </c>
+      <c r="G242" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H242" s="25"/>
+      <c r="I242" s="27">
+        <v>45457</v>
+      </c>
+      <c r="J242" s="26" t="s">
+        <v>508</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G193:H197">
@@ -9439,87 +9301,31 @@
   <mergeCells count="1">
     <mergeCell ref="C2:H2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G19:G35 G62 G69 G75 G77 G85 G89 G93:G95 G154:G190 G193 G200 G213:G219">
-    <cfRule type="cellIs" dxfId="23" priority="17" operator="equal">
+  <conditionalFormatting sqref="G19:G242">
+    <cfRule type="cellIs" dxfId="15" priority="5" operator="equal">
       <formula>"Невідомо"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="6" operator="equal">
       <formula>"Застосовно (з приміткою)"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="7" operator="equal">
       <formula>"Застосовно"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="8" operator="equal">
       <formula>"Не застосовно"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H11 H14:H15">
-    <cfRule type="cellIs" dxfId="31" priority="21" operator="equal">
+  <conditionalFormatting sqref="H9:H15">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
       <formula>"Невідомо"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
       <formula>"Застосовно (з приміткою)"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
       <formula>"Застосовно"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="24" operator="equal">
-      <formula>"Не застосовно"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H12">
-    <cfRule type="cellIs" dxfId="15" priority="13" operator="equal">
-      <formula>"Невідомо"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="14" operator="equal">
-      <formula>"Застосовно (з приміткою)"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="15" operator="equal">
-      <formula>"Застосовно"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="16" operator="equal">
-      <formula>"Не застосовно"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H9:H10">
-    <cfRule type="cellIs" dxfId="11" priority="9" operator="equal">
-      <formula>"Невідомо"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="10" operator="equal">
-      <formula>"Застосовно (з приміткою)"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
-      <formula>"Застосовно"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="12" operator="equal">
-      <formula>"Не застосовно"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G220:G241 G201:G212 G194:G199 G191:G192 G96:G153 G90:G92 G86:G88 G78:G84 G76 G70:G74 G63:G68 G36:G61">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
-      <formula>"Невідомо"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
-      <formula>"Застосовно (з приміткою)"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
-      <formula>"Застосовно"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
-      <formula>"Не застосовно"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
-      <formula>"Невідомо"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
-      <formula>"Застосовно (з приміткою)"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
-      <formula>"Застосовно"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
       <formula>"Не застосовно"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9756,16 +9562,16 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G3:G10">
-    <cfRule type="cellIs" dxfId="27" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
       <formula>"Невідомо"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"Застосовно (з приміткою)"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
       <formula>"Застосовно"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
       <formula>"Не застосовно"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Застосовне законодавство.xlsx
+++ b/Застосовне законодавство.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\користувач\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD2A989-A624-4835-8D86-402110D3BAEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C00C1A-79BA-4CD7-9E25-78200483B2FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{334805C5-B449-4CB8-AF80-1835CA06DE69}"/>
   </bookViews>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1288" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="601">
   <si>
     <t>- В цьому реєстрі перераховані тільки основні законодавчі акти, не враховуючи супутні акти, що затверджують зміни, або покладають завдання з реалізації, наприклад, Національної стратегії кібербезпеки.
 - Сайт ВРУ - основне джерело інформації, оскільки на ньому можна відстежувати актуальність законодавчих актів.</t>
@@ -2052,6 +2052,21 @@
   </si>
   <si>
     <t>Це Положення [..] визначає особливості їх функціонування та діяльності, а також здійснення Національним банком нагляду за їх діяльністю у разі настання особливого періоду.</t>
+  </si>
+  <si>
+    <t>Втратив чинність у зв'язку з Наказом Адміністрації Держспецзв’язку від 30.04.2024 № 228 від 28.01.2026 № 60.</t>
+  </si>
+  <si>
+    <t>Наказ Адміністрації Держспецзв’язку від 10.07.2024 №354</t>
+  </si>
+  <si>
+    <t>https://zakon.rada.gov.ua/rada/show/v0317519-24#Text</t>
+  </si>
+  <si>
+    <t>Наказ Адміністрації Держспецзв’язку від 24.06.2024 № 317</t>
+  </si>
+  <si>
+    <t>https://cip.gov.ua/ua/news/nakaz-administraciyi-derzhspeczv-yazku-vid-10-07-2024-354-pro-zatverdzhennya-rekomendacii-z-ocinki-dostatnosti-zakhodiv-zakhistu-informaciyi-kompleksnikh-sistem-zakhistu-informaciyi-v-informaciinikh-elektronnikh-komunikaciinikh-ta-informaciino-komunikaciinikh-sistemakh-stvorenikh-z-vikoristannyam-profiliv-bezpeki-informaciyi</t>
   </si>
 </sst>
 </file>
@@ -2151,7 +2166,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -2200,11 +2215,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2285,56 +2315,17 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="29">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <b/>
@@ -2832,6 +2823,13 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -2859,13 +2857,6 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -2903,6 +2894,51 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2917,21 +2953,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FE4F2F92-58E2-48B9-A7D4-627EBB6ED48E}" name="Таблиця2" displayName="Таблиця2" ref="B18:J242" totalsRowShown="0" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25">
-  <autoFilter ref="B18:J242" xr:uid="{FE4F2F92-58E2-48B9-A7D4-627EBB6ED48E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FE4F2F92-58E2-48B9-A7D4-627EBB6ED48E}" name="Таблиця2" displayName="Таблиця2" ref="B18:J243" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23" headerRowBorderDxfId="21" tableBorderDxfId="22">
+  <autoFilter ref="B18:J243" xr:uid="{FE4F2F92-58E2-48B9-A7D4-627EBB6ED48E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B19:I200">
     <sortCondition ref="B18:B200"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{DFA9E46C-509D-4A00-A369-7966EED6B176}" name="№" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{981014D8-EFBF-47F5-B054-36010B7987AF}" name="Джерело вимог" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{928FBB84-B24F-469A-AFD2-7EA49120BF89}" name="Посилання" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{D49602E6-E651-4C6D-8A88-C8DCD8A3AFDD}" name="Коментар" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{52AE3B44-6A02-4F51-99B9-C7E17C080BEC}" name="Категорія" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{DE39899F-E232-40DC-A0D1-10B3A973A842}" name="Застосовність" dataDxfId="19"/>
-    <tableColumn id="10" xr3:uid="{40F3EA47-8E92-48F7-A24A-6369E84EA096}" name="Теги" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{A1D4F9E4-94BB-4008-834E-B5DC4DE59C40}" name="Дата прийняття" dataDxfId="17"/>
-    <tableColumn id="7" xr3:uid="{2B27F073-AE91-4210-B0D6-642DEFE05F63}" name="Галузь" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{DFA9E46C-509D-4A00-A369-7966EED6B176}" name="№" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{981014D8-EFBF-47F5-B054-36010B7987AF}" name="Джерело вимог" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{928FBB84-B24F-469A-AFD2-7EA49120BF89}" name="Посилання" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{D49602E6-E651-4C6D-8A88-C8DCD8A3AFDD}" name="Коментар" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{52AE3B44-6A02-4F51-99B9-C7E17C080BEC}" name="Категорія" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{DE39899F-E232-40DC-A0D1-10B3A973A842}" name="Застосовність" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{40F3EA47-8E92-48F7-A24A-6369E84EA096}" name="Теги" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{A1D4F9E4-94BB-4008-834E-B5DC4DE59C40}" name="Дата прийняття" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{2B27F073-AE91-4210-B0D6-642DEFE05F63}" name="Галузь" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3234,7 +3270,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B971BF4-F5CF-496D-9610-E7CBA5A28B9C}">
-  <dimension ref="A2:J242"/>
+  <dimension ref="A2:J244"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
@@ -7019,12 +7055,14 @@
       <c r="D153" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="E153" s="7"/>
+      <c r="E153" s="7" t="s">
+        <v>596</v>
+      </c>
       <c r="F153" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="G153" s="3" t="s">
-        <v>10</v>
+      <c r="G153" s="23" t="s">
+        <v>579</v>
       </c>
       <c r="H153" s="7" t="s">
         <v>26</v>
@@ -9268,30 +9306,75 @@
       <c r="J241" s="10"/>
     </row>
     <row r="242" spans="2:10" ht="207" x14ac:dyDescent="0.25">
-      <c r="B242" s="25">
+      <c r="B242" s="7">
         <v>224</v>
       </c>
-      <c r="C242" s="25" t="s">
+      <c r="C242" s="7" t="s">
         <v>594</v>
       </c>
-      <c r="D242" s="25" t="s">
+      <c r="D242" s="7" t="s">
         <v>593</v>
       </c>
-      <c r="E242" s="25" t="s">
+      <c r="E242" s="7" t="s">
         <v>595</v>
       </c>
-      <c r="F242" s="25" t="s">
+      <c r="F242" s="7" t="s">
         <v>498</v>
       </c>
       <c r="G242" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H242" s="25"/>
-      <c r="I242" s="27">
+      <c r="H242" s="7"/>
+      <c r="I242" s="14">
         <v>45457</v>
       </c>
-      <c r="J242" s="26" t="s">
+      <c r="J242" s="15" t="s">
         <v>508</v>
+      </c>
+    </row>
+    <row r="243" spans="2:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B243" s="25">
+        <v>225</v>
+      </c>
+      <c r="C243" s="25" t="s">
+        <v>597</v>
+      </c>
+      <c r="D243" s="25" t="s">
+        <v>600</v>
+      </c>
+      <c r="E243" s="25"/>
+      <c r="F243" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="G243" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H243" s="25"/>
+      <c r="I243" s="27">
+        <v>45483</v>
+      </c>
+      <c r="J243" s="26"/>
+    </row>
+    <row r="244" spans="2:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B244" s="28">
+        <v>226</v>
+      </c>
+      <c r="C244" s="28" t="s">
+        <v>599</v>
+      </c>
+      <c r="D244" s="28" t="s">
+        <v>598</v>
+      </c>
+      <c r="E244" s="28"/>
+      <c r="F244" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="G244" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H244" s="28"/>
+      <c r="I244" s="29">
+        <v>45467</v>
       </c>
     </row>
   </sheetData>
@@ -9301,31 +9384,31 @@
   <mergeCells count="1">
     <mergeCell ref="C2:H2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G19:G242">
-    <cfRule type="cellIs" dxfId="15" priority="5" operator="equal">
+  <conditionalFormatting sqref="G19:G244">
+    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
       <formula>"Невідомо"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="6" operator="equal">
       <formula>"Застосовно (з приміткою)"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="7" operator="equal">
       <formula>"Застосовно"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
       <formula>"Не застосовно"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9:H15">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"Невідомо"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"Застосовно (з приміткою)"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
       <formula>"Застосовно"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
       <formula>"Не застосовно"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9562,16 +9645,16 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G3:G10">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
       <formula>"Невідомо"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="6" operator="equal">
       <formula>"Застосовно (з приміткою)"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
       <formula>"Застосовно"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="8" operator="equal">
       <formula>"Не застосовно"</formula>
     </cfRule>
   </conditionalFormatting>
